--- a/link_convenios.xlsx
+++ b/link_convenios.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\CGE\bi_atualizacao\portal_convenios_entrada\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,7 +15,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$1383</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$1424</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2378" uniqueCount="1073">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2541" uniqueCount="1154">
   <si>
     <t>https://drive.google.com/file/d/1mnH14gEK5_xghzIJ-rHHZ8lOxqCsVnB8/view</t>
   </si>
@@ -2764,63 +2764,21 @@
     <t>https://drive.google.com/file/d/1H24l11X3QGrWdfvoZynQ9ZN-a1D1iPiT/view</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1eTyUtNmidce8ThMst8ZT1RyrtE5eZxfq/view</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1CxnA7dcCqOBOTyo9hNCWW5khzTi4u-fo/view</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/13TMYPI3sOFkieKbvNGXTdu6iE-z7vZ-N/view</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/16O0LX2aR_PJzjlnBKuww1600gnd_V6B2/view</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/14E0_U-6XuBuOkPpE5Szpk11Bc58KHP4G/view</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1-kRCqVHqtMgKQf6QqQJ3n0x-zNfWZTKX/view</t>
   </si>
   <si>
     <t>https://drive.google.com/file/d/13vrg6XFHUrFAQsGmuk2DP_xLtJ4L21Bn/view</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1sTOnkMjg51EEz5Vt5m1Q4kraOOysUHvC/view</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1xbd53caMATqjhhjqYYZG0O2PNm13iKd7/view</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1T6ZETEGr-iTOKn6dH5DghyszPkddJNY7/view</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1N0vNU5lROA6-1o-88NJx3Z3zIPcUsUHu/view</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/14zStlv7BVLn0I1InKamygs5yEdR0Cck_/view</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/17nlj3PnxB0xtjY_HCGapjo0baAFjUdV4/view</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1uFCwQE4CZ-1juFWF7v9gvRUBPrlZ0Mfu/view</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1Uz7b7U1NGfc6mWM0gVP-jvgt9CAO1BvG/view</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1XV2o748j_6ntOofh6ZvTiXR91GfyjdMA/view</t>
   </si>
   <si>
     <t>https://drive.google.com/file/d/1Bg_UNQf668Le8owp5v6coL0f-3TleE3H/view</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1raZ5_8BD13QT2ZJJA3IYOnNKWcXReyVF/view</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/10py08rhNmQtjiMwF6SD2IOZI23K_xzN9/view</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1GYHAPorXGL8dLsTueQr3knV423FD3nsU/view</t>
   </si>
   <si>
@@ -2836,9 +2794,6 @@
     <t>https://drive.google.com/file/d/15M32iqPLvdpvRsvnr9kEGignRFcKt-xJ/view</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1be5p1WC1VoXqsUWM5QqGrII2fmJ4-__s/view</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1c30KPwk28ct1FLIhSUmebY2t3HuAs8xr/view</t>
   </si>
   <si>
@@ -2848,9 +2803,6 @@
     <t>https://drive.google.com/file/d/19A6z8_P5Gvdmhv1Lv_-NUm8Dayy8Yda3/view</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/10dM6o2xBIkawwESeixeJB-C-pOc2hS_m/view</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1TASVbrz7b5trWIYGXbluyn8H1ObT4Yu6/view</t>
   </si>
   <si>
@@ -2881,18 +2833,12 @@
     <t>https://drive.google.com/file/d/1Ic-OohL6PkFXRaPaOs94G3PG5Df00Q-z/view</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1aqZvXgE6gWoGqEXopDwxdfkIuV90jJKx/view</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/158gGeaZPwg0xuLdS7w67hT4UuBR_YNqW/view</t>
   </si>
   <si>
     <t>https://drive.google.com/file/d/1UB32aNda3kLvK72HwflBNaQcBNbUWHde/view</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/14MW5oMcPrezHla-WPwXR2G5NnXKTcWz8/view</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/11Q-MB7_B24PEGiojkydfVK5iiJIKwJfb/view</t>
   </si>
   <si>
@@ -2902,21 +2848,9 @@
     <t>https://drive.google.com/file/d/14GCNZOGi2pXwqrk6YoYtEtXi2DMnBr64/view</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1vqEO-JdsnifBgX1mZZMsA_eDguqfYSMo/view</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1K9e0KMdyNs_vvlf6Ir30cZNHmKoJdxhT/view</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1IQKdSg-GNNA5p10--AqfZkmb4dtM9Zb2/view</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1jXpVMPthQlDcxqddInntciHpBXIKDfTb/view</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1R9aKfMahCJzUMEbGlm91RK64qbD1rBu0/view</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1SHv4cHJIFlOnSg3YgscNtckzre9xmpYA/view</t>
   </si>
   <si>
@@ -2926,24 +2860,12 @@
     <t>https://drive.google.com/file/d/1tQNJmQvnYwhXVEALtgLPi4NTPSDX243z/view</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/19FnM53Bv6eEeqlBnmz2IqkTwtd07_Pme/view</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1GrGns9Ds6lPc3BhEVsG5663UjB-1cznS/view</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1UR0tRtKN8K5qkRrYp4GfJbmh72yF6-VA/view</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1sV-YOoHKTtSF6BOV1mvQLU1uAHURYmXJ/view</t>
   </si>
   <si>
     <t>https://drive.google.com/file/d/1e6gPnYR2Ls_5mzrHYiqDTpWKNAn_3m06/view</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1MHsPtBg7P4Imf9jU0cS_KZMJOjhAFBYn/view</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1x8TEZhRFySS_YlHrpyDs6NzhPa1ReJs0/view</t>
   </si>
   <si>
@@ -2953,18 +2875,6 @@
     <t>https://drive.google.com/file/d/1DNWJHXfpKqkZEoFTdj2db9cE8qOOH0xu/view</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1vPoKqp1Zn7YdG_w2ipsxLgrSKhCptW4I/view</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1PQTjHqAsH2dCaRWEG1GRvlCrnGsSJgoc/view</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1Wwbsj21NOO5R5sBjPQHP_t2rWL3IDH8l/view</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1gb2gj-6yxScC4_dM6mDwyQBLcYBPwV_a/view</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1ohuuGicd2b6NzQsbvSq3EqkoVyvfdDQs/view</t>
   </si>
   <si>
@@ -2977,9 +2887,6 @@
     <t>https://drive.google.com/file/d/1zwmM9HINmpZGknlFA09DcjvIu-C8YtdS/view</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1v0uSaHJ89fd6g57dnO8YbKIw7cKicc5m/view</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/19d9481XoqpJQ2KuAIk7EOWBRfY8TWtCx/view</t>
   </si>
   <si>
@@ -2989,9 +2896,6 @@
     <t>https://drive.google.com/file/d/1pWIyFIkhuoITcht45Ui65CXeOp0h726I/view</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1RXAVWGM7BrDGFIPNnr5Se7AgOlp394ci/view</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1HNxIQS51qr5xydjx1zUlgZpD-bXIX27s/view</t>
   </si>
   <si>
@@ -3013,15 +2917,9 @@
     <t>https://drive.google.com/file/d/1zIZV0zfFCXc9mDpv2nPJ8c39CkPpenfu/view</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/17qqIsu-G5GoTjvL97LC7t-X4VKnXmxEA/view</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1ciwBeey23ViTZLPSb1C4cqy2w941sdIP/view</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1YkdAFZ3m7jLRvNAjQTGCdMW8YNSgISNS/view</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1_fK_0RVgdQcmD5VY-r7vmtbyfk5oR6fr/view</t>
   </si>
   <si>
@@ -3031,12 +2929,6 @@
     <t>https://drive.google.com/file/d/11S5FdwMAnj7rW5X9tbPswpeHsO7HQ-Wn/view</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1ZuvWk48eS2Obi3uI2Q1S3hrLtE998n47/view</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1zsXRhmuH4inOazJJ8Xlv44md5vuFNULS/view</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1yg9t0V07qnUXhhNWcSOr2dSUIoA8mw3b/view</t>
   </si>
   <si>
@@ -3082,9 +2974,6 @@
     <t>https://drive.google.com/file/d/1MSs7n7A-A9y0Nt6Tkup5hen7dctgWyXP/view</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/16QJAGKlWU5rQPOiZK-wXc9dhMi50vn-1/view</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1j08vTVlyMZDO8N-LU-JcRSxU2Jy9yRQy/view</t>
   </si>
   <si>
@@ -3106,15 +2995,9 @@
     <t>https://especiais.transferegov.sistema.gov.br/transferencia-especial/plano-acao/detalhe/92173/plano-trabalho</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1mfDBlb0eKkEMMlo04PFLyzEi8wywqQZ-/view</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1r5AjYrp90Im_ufCn4BuikSZMWNlxCBbW/view</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1tbZ4LGgPfQbeo5cBumF8xwHPxADfvPbX/view</t>
-  </si>
-  <si>
     <t>https://especiais.transferegov.sistema.gov.br/transferencia-especial/plano-acao/detalhe/85246/plano-trabalho</t>
   </si>
   <si>
@@ -3260,13 +3143,373 @@
   </si>
   <si>
     <t>https://discricionarias.transferegov.sistema.gov.br/voluntarias/ConsultarProposta/ResultadoDaConsultaDePropostaDetalharProposta.do?idProposta=2177938&amp;Usr=guest&amp;Pwd=guest</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/nHtxeNPHerW9Bwf</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/7doQyHAHCpyKf8k</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/cgoif9Jr9ComLJM</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/Znmao5aHrTCHa8Y</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/s69YnE6R43rBbYf</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/4JHaQ5BNqwFdn3E</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/jEdFZ4niYoY3CzF</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/nyJckzoBAJg5toB</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/KMi7mg3KECosw5M</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/3zCSkzrrifZDDfT</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/wjtRy3c8WWirzmK</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/6pWqgLB6pckHCgq</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/8sqBzf4wmEPCM5b</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/y8TPwt35eDozefw</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/scJYMzZeJXNamyP</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/fZwMnHaPZmLbFN7</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/BxxcrxXYNs2J5kC</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/qJ24QSiDtDCEYck</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/SQDLjnnCscF2NiK</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/JyEGYtoiL5Z3eLA</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/Nttgd8ftHofRfQ3</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/EYbLJR9XpBCK5Mp</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/bEtbTdNN9ABeTYk</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/3FQG4Pttcdjwd4W</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/P6BWccmofBrdDKB</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/F5ygwTsLcA5zs9W</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/twwpZoBmMMo29ND</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/f6DX8qsMa2ZFnXC</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/6SHjaENQ8WzeNKm</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/2BKBZZYKkbDy5To</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/CbEY5dkpKxQoLaf</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/2LFSaLoej8TiwX2</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/QDoM3p9o3g6BRCW</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/waTXCQfLsQPEr2F</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/afk9PHNqQZ6dr7e</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/fKEG4R9CWmfQjcY</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/rJWZp6bJ8Xpbxwr</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/mZXcM48WwpxxpXc</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/jdPnnq7HAFrZxH2</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/efKs6CFYdN6TnPb</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/6P3pnywrwx6rzT9</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/qHCyeRj2GrK3aQF</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/mMALi3t2a4RE8qd</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/zByWiSCofCZAcwz</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/AL8S2FYzmifJqxz</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/dEMdbowe2bNoEot</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/Abj2QjaxxTxtPEg</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/iGC3aBEgen4MfP5</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/qncX7CaPMmkybkG</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/SqwoLoMcFjpc9F2</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/PHRGnPwj6bc9KPr</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/SxNdcKpK8RymnCi</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/LSH9BkDajmGdiC3</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/2Scrp9BQAzd4fGM</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/nCPkaCXxqJzro4s</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/mo5MG6GZ5nXECAG</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/aQRfwRwikATPHcJ</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/RD5CX4Fi7D2Rtc7</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/2fx2pskmwKdmw85</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/7AqqkyzXPW7N767</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/JAbPYepAR7zfnmF</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/8KxyYTWHGB56qti</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/W8dSFbQnt23WPc3</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/Di6Bq5Xt9Xp5riD</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/BWjRSz5sWpT3ExP</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/6C5omwzy7SKz6ZG</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/ZG2zDGPAicd37Yd</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/iWfDMA3yLQqdxCS</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/qpxi3WkexcbDzqL</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/zRL3GNgjzbDya8r</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/MPrei8Em39dXL7t</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/R7PwYFz4siGEXZ8</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/M3HCAqMkBNbXwQY</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/FjJzeaFbFxMR9GJ</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/iGkz552LD7ecfsW</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/xfpE79mb4dp8JsH</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/eXtaszzYwZgeBi8</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/CinMeeAno2YSEqz</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/DNoiWeTLmCKjByw</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/DrspZYocMpAcPSg</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/mEAH4yLEeF9jK5Q</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/q7tziRGLHKtcBq5</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/5aE3WrTE67wwwaS</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/11GIREdwbs7LMkFKiFc7zYq41YEy0G6Mb/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1tmlDUUN9sGZDeajigymVzwAOi-Y84Pka/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1A8M760Xvg19thV6B0javhwgZ-XUt8Noc/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1a1Hs-M3xUako8ZOnfz0aH-MoTuT85psW/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bmr56fg5KvejtfQEO31tdwf8JBZCv2Z7/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1MhQzlecysinwQypM1n_zcskCltX-G7Fo/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1LKL0VN7R-nS2jtgmDy_qulz7cjYgOIOf/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1pn3JuYbUiKAP5Fgve3RsWQmu7HnwQYyR/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1hztl9LGtuubjCrVYIZCxpEaeiCBg7P_Y/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1HGSqeWaVtPRyFzk6QVzM-0d8wK23AZ_k/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ch6dAMphD9GUSTRvsEbC3xJdZ9IVQqQ_/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1BQUK6l-_SRgr4cxIVW0Ape3uAsKaW_VY/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1V-6syuuRwUnVU1Dz6ICKRP-isnE0tCia/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1z52rww-QRI6cW3gAdobH7rEV1akJlgFw/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/18ps4ZUfMF3fJgH6lthY1PchqdYjFYlPZ/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1IRRKe7f0fEh_dJpHHkrA3sh5uTo-b5w2/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1xZ4suaA9X_A0C_nk7x6BvT5j4A1CZRYQ/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1-wOGs3hQhQbmQLQ0zcJzk9sAf8Qb9NrS/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/15tu9A1EIIPzl0vTNyDDs5nlxWUJZD13K/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1hU8etDwnawFANq3TCtM-LugUx3fDF7Tr/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1XWpHyKWOlkFt3bZSKeOCiLwnH5YDi7JO/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1zaXXCxxzvs3zS2awICpOpMpViZ6ut-Wj/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1lqPif7mjIkeKv4UrwAxvCd9AogjQKlOL/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1tkyFeoaVNXCAy0MJSVbfJnAJtyVH9-3Y/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1r8wqjYNVTz_Aj7aqRFAdJC9KObwQgMUO/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1HhDPQbFv7YkDHRu5_Yy3dRlVmdKycYZA/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1WZUSqJq-pYWRWnY6p0hFGueuKXiPph1U/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1RlsX5G7LIVBzieECwDRFtN_8nDx_W19n/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1g2Y6oejdjnKyv71fVddG5RPRVu92vte6/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/10GKkifG2dNitLQe8x3Cgz8jrhwu9cqP5/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ax_D8qnfFhsZXYHOl6fcf1GSp22oJkd8/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Ez-fFHa9xYsc-Wq31y1m56JabET7mrwQ/view</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1MPDAU1yAEIyTEt7-SFKo2NejDhqNUj2O/view</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/3je8MbXPHTMPiH2</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/ezRekmfGzw7TqS4</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/FdP7CXTxzcXJnn4</t>
+  </si>
+  <si>
+    <t>https://nuvem.cge.mg.gov.br/index.php/s/wyiceeaoCd2nQbD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3279,18 +3522,6 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Tahoma"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3300,7 +3531,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -3323,44 +3554,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3693,14 +3897,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1383"/>
+  <dimension ref="A1:C1424"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="76.5" customWidth="1"/>
     <col min="3" max="3" width="17.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15">
+    <row r="1" spans="1:3" ht="15">
       <c r="A1" s="1" t="s">
         <v>707</v>
       </c>
@@ -3710,9 +3914,8 @@
       <c r="C1" t="s">
         <v>890</v>
       </c>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>9270124</v>
       </c>
@@ -3723,7 +3926,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>9270144</v>
       </c>
@@ -3734,7 +3937,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>9270149</v>
       </c>
@@ -3745,7 +3948,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>9270192</v>
       </c>
@@ -3756,7 +3959,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>9270199</v>
       </c>
@@ -3767,7 +3970,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>9270223</v>
       </c>
@@ -3778,7 +3981,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>9270245</v>
       </c>
@@ -3789,7 +3992,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>9270257</v>
       </c>
@@ -3800,13 +4003,12 @@
         <v>891</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>9270525</v>
       </c>
-      <c r="B10" s="6"/>
-    </row>
-    <row r="11" spans="1:4">
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>9270802</v>
       </c>
@@ -3817,7 +4019,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>9270942</v>
       </c>
@@ -3828,7 +4030,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>9270958</v>
       </c>
@@ -3839,7 +4041,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:3">
       <c r="A14">
         <v>9271592</v>
       </c>
@@ -3850,7 +4052,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:3">
       <c r="A15">
         <v>9271602</v>
       </c>
@@ -3861,7 +4063,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:3">
       <c r="A16">
         <v>9271647</v>
       </c>
@@ -3876,17 +4078,16 @@
       <c r="A17">
         <v>9271652</v>
       </c>
-      <c r="B17" s="6"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
         <v>9273925</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>908</v>
+      <c r="B18" t="s">
+        <v>1110</v>
       </c>
       <c r="C18" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3898,19 +4099,16 @@
       <c r="A20">
         <v>9274432</v>
       </c>
-      <c r="B20" s="6"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
         <v>9274435</v>
       </c>
-      <c r="B21" s="6"/>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
         <v>9274436</v>
       </c>
-      <c r="B22" s="6"/>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
@@ -3926,7 +4124,6 @@
       <c r="A25">
         <v>9274476</v>
       </c>
-      <c r="B25" s="6"/>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
@@ -3937,7 +4134,7 @@
       <c r="A27">
         <v>9274488</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" t="s">
         <v>706</v>
       </c>
       <c r="C27" t="s">
@@ -3970,7 +4167,12 @@
       <c r="A30">
         <v>9275414</v>
       </c>
-      <c r="B30" s="6"/>
+      <c r="B30" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C30" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
@@ -3987,6 +4189,12 @@
       <c r="A32">
         <v>9275644</v>
       </c>
+      <c r="B32" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C32" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
@@ -4003,7 +4211,7 @@
         <v>9276279</v>
       </c>
       <c r="B35" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C35" t="s">
         <v>899</v>
@@ -4056,7 +4264,6 @@
       <c r="A41">
         <v>9277463</v>
       </c>
-      <c r="B41" s="6"/>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
@@ -4073,6 +4280,12 @@
       <c r="A43">
         <v>9279438</v>
       </c>
+      <c r="B43" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C43" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
@@ -4111,14 +4324,13 @@
       <c r="A47">
         <v>9280531</v>
       </c>
-      <c r="B47" s="6"/>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
         <v>9280770</v>
       </c>
       <c r="B48" t="s">
-        <v>910</v>
+        <v>1035</v>
       </c>
       <c r="C48" t="s">
         <v>891</v>
@@ -4128,13 +4340,11 @@
       <c r="A49">
         <v>9282800</v>
       </c>
-      <c r="B49" s="6"/>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
         <v>9282801</v>
       </c>
-      <c r="B50" s="6"/>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
@@ -4145,7 +4355,6 @@
       <c r="A52">
         <v>9282804</v>
       </c>
-      <c r="B52" s="6"/>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
@@ -4156,7 +4365,6 @@
       <c r="A54">
         <v>9282908</v>
       </c>
-      <c r="B54" s="6"/>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
@@ -4211,13 +4419,17 @@
       <c r="A60">
         <v>9283222</v>
       </c>
-      <c r="B60" s="6"/>
+      <c r="B60" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C60" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
         <v>9283548</v>
       </c>
-      <c r="B61" s="6"/>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
@@ -4239,7 +4451,6 @@
       <c r="A64">
         <v>9286365</v>
       </c>
-      <c r="B64" s="6"/>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
@@ -4257,7 +4468,7 @@
         <v>9286435</v>
       </c>
       <c r="B66" t="s">
-        <v>911</v>
+        <v>1106</v>
       </c>
       <c r="C66" t="s">
         <v>891</v>
@@ -4267,12 +4478,17 @@
       <c r="A67">
         <v>9288037</v>
       </c>
-      <c r="B67" s="6"/>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
         <v>9288047</v>
       </c>
+      <c r="B68" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C68" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
@@ -4290,7 +4506,7 @@
         <v>9288059</v>
       </c>
       <c r="B70" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="C70" t="s">
         <v>891</v>
@@ -5335,7 +5551,7 @@
         <v>9291916</v>
       </c>
       <c r="B165" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="C165" t="s">
         <v>891</v>
@@ -5345,7 +5561,12 @@
       <c r="A166">
         <v>9291958</v>
       </c>
-      <c r="B166" s="6"/>
+      <c r="B166" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C166" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167">
@@ -5444,12 +5665,23 @@
       <c r="A176">
         <v>9292047</v>
       </c>
+      <c r="B176" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C176" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177">
         <v>9292050</v>
       </c>
-      <c r="B177" s="6"/>
+      <c r="B177" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C177" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178">
@@ -5477,7 +5709,12 @@
       <c r="A180">
         <v>9292803</v>
       </c>
-      <c r="B180" s="6"/>
+      <c r="B180" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C180" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181">
@@ -5543,13 +5780,11 @@
       <c r="A187">
         <v>9292953</v>
       </c>
-      <c r="B187" s="6"/>
     </row>
     <row r="188" spans="1:3">
       <c r="A188">
         <v>9292955</v>
       </c>
-      <c r="B188" s="6"/>
     </row>
     <row r="189" spans="1:3">
       <c r="A189">
@@ -5567,7 +5802,7 @@
         <v>9292962</v>
       </c>
       <c r="B190" t="s">
-        <v>914</v>
+        <v>1062</v>
       </c>
       <c r="C190" t="s">
         <v>891</v>
@@ -5589,7 +5824,7 @@
         <v>9293658</v>
       </c>
       <c r="B192" t="s">
-        <v>915</v>
+        <v>1053</v>
       </c>
       <c r="C192" t="s">
         <v>891</v>
@@ -5644,7 +5879,7 @@
         <v>9293702</v>
       </c>
       <c r="B197" t="s">
-        <v>916</v>
+        <v>1055</v>
       </c>
       <c r="C197" t="s">
         <v>891</v>
@@ -5665,8 +5900,8 @@
       <c r="A199">
         <v>9294166</v>
       </c>
-      <c r="B199" s="4" t="s">
-        <v>1026</v>
+      <c r="B199" t="s">
+        <v>987</v>
       </c>
       <c r="C199" t="s">
         <v>899</v>
@@ -5775,13 +6010,19 @@
       <c r="A209">
         <v>9309074</v>
       </c>
+      <c r="B209" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C209" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210">
         <v>9309930</v>
       </c>
       <c r="B210" t="s">
-        <v>917</v>
+        <v>1093</v>
       </c>
       <c r="C210" t="s">
         <v>891</v>
@@ -5880,7 +6121,7 @@
         <v>9313581</v>
       </c>
       <c r="B219" t="s">
-        <v>918</v>
+        <v>1068</v>
       </c>
       <c r="C219" t="s">
         <v>891</v>
@@ -5912,7 +6153,12 @@
       <c r="A222">
         <v>9314597</v>
       </c>
-      <c r="B222" s="6"/>
+      <c r="B222" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C222" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223">
@@ -5929,7 +6175,12 @@
       <c r="A224">
         <v>9315152</v>
       </c>
-      <c r="B224" s="6"/>
+      <c r="B224" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C224" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
@@ -5980,18 +6231,18 @@
         <v>9315345</v>
       </c>
       <c r="B229" t="s">
-        <v>919</v>
+        <v>1045</v>
       </c>
       <c r="C229" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230">
         <v>9315346</v>
       </c>
-      <c r="B230" s="4" t="s">
-        <v>920</v>
+      <c r="B230" t="s">
+        <v>1071</v>
       </c>
       <c r="C230" t="s">
         <v>891</v>
@@ -6012,7 +6263,12 @@
       <c r="A232">
         <v>9315482</v>
       </c>
-      <c r="B232" s="6"/>
+      <c r="B232" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C232" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233">
@@ -6040,13 +6296,17 @@
       <c r="A235">
         <v>9315532</v>
       </c>
-      <c r="B235" s="6"/>
     </row>
     <row r="236" spans="1:3">
       <c r="A236">
         <v>9315629</v>
       </c>
-      <c r="B236" s="6"/>
+      <c r="B236" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C236" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237">
@@ -6074,7 +6334,6 @@
       <c r="A239">
         <v>9317170</v>
       </c>
-      <c r="B239" s="6"/>
     </row>
     <row r="240" spans="1:3">
       <c r="A240">
@@ -6085,14 +6344,13 @@
       <c r="A241">
         <v>9317173</v>
       </c>
-      <c r="B241" s="6"/>
     </row>
     <row r="242" spans="1:3">
       <c r="A242">
         <v>9317262</v>
       </c>
       <c r="B242" t="s">
-        <v>921</v>
+        <v>1103</v>
       </c>
       <c r="C242" t="s">
         <v>891</v>
@@ -6201,7 +6459,12 @@
       <c r="A252">
         <v>9317875</v>
       </c>
-      <c r="B252" s="6"/>
+      <c r="B252" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C252" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="253" spans="1:3">
       <c r="A253">
@@ -6212,13 +6475,19 @@
       <c r="A254">
         <v>9317884</v>
       </c>
+      <c r="B254" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C254" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255">
         <v>9317959</v>
       </c>
       <c r="B255" t="s">
-        <v>922</v>
+        <v>910</v>
       </c>
       <c r="C255" t="s">
         <v>891</v>
@@ -6229,7 +6498,7 @@
         <v>9317965</v>
       </c>
       <c r="B256" t="s">
-        <v>923</v>
+        <v>911</v>
       </c>
       <c r="C256" t="s">
         <v>891</v>
@@ -6239,43 +6508,36 @@
       <c r="A257">
         <v>9317966</v>
       </c>
-      <c r="B257" s="6"/>
     </row>
     <row r="258" spans="1:3">
       <c r="A258">
         <v>9318254</v>
       </c>
-      <c r="B258" s="6"/>
     </row>
     <row r="259" spans="1:3">
       <c r="A259">
         <v>9318261</v>
       </c>
-      <c r="B259" s="6"/>
     </row>
     <row r="260" spans="1:3">
       <c r="A260">
         <v>9318425</v>
       </c>
-      <c r="B260" s="6"/>
     </row>
     <row r="261" spans="1:3">
       <c r="A261">
         <v>9318431</v>
       </c>
-      <c r="B261" s="6"/>
     </row>
     <row r="262" spans="1:3">
       <c r="A262">
         <v>9318432</v>
       </c>
-      <c r="B262" s="6"/>
     </row>
     <row r="263" spans="1:3">
       <c r="A263">
         <v>9318433</v>
       </c>
-      <c r="B263" s="6"/>
     </row>
     <row r="264" spans="1:3">
       <c r="A264">
@@ -6326,7 +6588,7 @@
         <v>9318754</v>
       </c>
       <c r="B268" t="s">
-        <v>924</v>
+        <v>1113</v>
       </c>
       <c r="C268" t="s">
         <v>891</v>
@@ -6369,31 +6631,40 @@
       <c r="A272">
         <v>9318771</v>
       </c>
+      <c r="B272" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C272" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273">
         <v>9318789</v>
       </c>
-      <c r="B273" s="6"/>
     </row>
     <row r="274" spans="1:3">
       <c r="A274">
         <v>9318792</v>
       </c>
-      <c r="B274" s="6"/>
+      <c r="B274" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C274" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="275" spans="1:3">
       <c r="A275">
         <v>9318794</v>
       </c>
-      <c r="B275" s="6"/>
     </row>
     <row r="276" spans="1:3">
       <c r="A276">
         <v>9319127</v>
       </c>
       <c r="B276" t="s">
-        <v>925</v>
+        <v>1078</v>
       </c>
       <c r="C276" t="s">
         <v>891</v>
@@ -6403,14 +6674,13 @@
       <c r="A277">
         <v>9319164</v>
       </c>
-      <c r="B277" s="6"/>
     </row>
     <row r="278" spans="1:3">
       <c r="A278">
         <v>9319167</v>
       </c>
       <c r="B278" t="s">
-        <v>926</v>
+        <v>912</v>
       </c>
       <c r="C278" t="s">
         <v>891</v>
@@ -6421,7 +6691,7 @@
         <v>9319176</v>
       </c>
       <c r="B279" t="s">
-        <v>927</v>
+        <v>913</v>
       </c>
       <c r="C279" t="s">
         <v>891</v>
@@ -6464,7 +6734,6 @@
       <c r="A283">
         <v>9319205</v>
       </c>
-      <c r="B283" s="6"/>
     </row>
     <row r="284" spans="1:3">
       <c r="A284">
@@ -6601,7 +6870,6 @@
       <c r="A297">
         <v>9322343</v>
       </c>
-      <c r="B297" s="6"/>
     </row>
     <row r="298" spans="1:3">
       <c r="A298">
@@ -6618,14 +6886,13 @@
       <c r="A299">
         <v>9322363</v>
       </c>
-      <c r="B299" s="6"/>
     </row>
     <row r="300" spans="1:3">
       <c r="A300">
         <v>9323059</v>
       </c>
       <c r="B300" t="s">
-        <v>928</v>
+        <v>914</v>
       </c>
       <c r="C300" t="s">
         <v>897</v>
@@ -6640,7 +6907,6 @@
       <c r="A302">
         <v>9323116</v>
       </c>
-      <c r="B302" s="6"/>
     </row>
     <row r="303" spans="1:3">
       <c r="A303">
@@ -6656,13 +6922,11 @@
       <c r="A305">
         <v>9323280</v>
       </c>
-      <c r="B305" s="6"/>
     </row>
     <row r="306" spans="1:3">
       <c r="A306">
         <v>9323281</v>
       </c>
-      <c r="B306" s="6"/>
     </row>
     <row r="307" spans="1:3">
       <c r="A307">
@@ -6673,7 +6937,6 @@
       <c r="A308">
         <v>9323284</v>
       </c>
-      <c r="B308" s="6"/>
     </row>
     <row r="309" spans="1:3">
       <c r="A309">
@@ -6691,7 +6954,7 @@
         <v>9323554</v>
       </c>
       <c r="B310" t="s">
-        <v>929</v>
+        <v>915</v>
       </c>
       <c r="C310" t="s">
         <v>891</v>
@@ -6746,7 +7009,7 @@
         <v>9324184</v>
       </c>
       <c r="B315" t="s">
-        <v>930</v>
+        <v>916</v>
       </c>
       <c r="C315" t="s">
         <v>891</v>
@@ -6800,7 +7063,6 @@
       <c r="A320">
         <v>9325273</v>
       </c>
-      <c r="B320" s="6"/>
     </row>
     <row r="321" spans="1:3">
       <c r="A321">
@@ -6866,6 +7128,12 @@
       <c r="A327">
         <v>9325892</v>
       </c>
+      <c r="B327" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C327" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328">
@@ -6882,8 +7150,8 @@
       <c r="A329">
         <v>9326072</v>
       </c>
-      <c r="B329" s="4" t="s">
-        <v>931</v>
+      <c r="B329" t="s">
+        <v>1075</v>
       </c>
       <c r="C329" t="s">
         <v>891</v>
@@ -6893,7 +7161,12 @@
       <c r="A330">
         <v>9326074</v>
       </c>
-      <c r="B330" s="6"/>
+      <c r="B330" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C330" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331">
@@ -6904,8 +7177,8 @@
       <c r="A332">
         <v>9326079</v>
       </c>
-      <c r="B332" s="4" t="s">
-        <v>932</v>
+      <c r="B332" t="s">
+        <v>917</v>
       </c>
       <c r="C332" t="s">
         <v>897</v>
@@ -6916,7 +7189,7 @@
         <v>9326080</v>
       </c>
       <c r="B333" t="s">
-        <v>933</v>
+        <v>918</v>
       </c>
       <c r="C333" t="s">
         <v>897</v>
@@ -6937,13 +7210,17 @@
       <c r="A335">
         <v>9327299</v>
       </c>
-      <c r="B335" s="6"/>
     </row>
     <row r="336" spans="1:3">
       <c r="A336">
         <v>9327338</v>
       </c>
-      <c r="B336" s="6"/>
+      <c r="B336" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C336" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="337" spans="1:3">
       <c r="A337">
@@ -7048,7 +7325,6 @@
       <c r="A346">
         <v>9327388</v>
       </c>
-      <c r="B346" s="6"/>
     </row>
     <row r="347" spans="1:3">
       <c r="A347">
@@ -7077,7 +7353,7 @@
         <v>9327450</v>
       </c>
       <c r="B349" t="s">
-        <v>934</v>
+        <v>919</v>
       </c>
       <c r="C349" t="s">
         <v>891</v>
@@ -7114,14 +7390,13 @@
       <c r="A353">
         <v>9328339</v>
       </c>
-      <c r="B353" s="6"/>
     </row>
     <row r="354" spans="1:3">
       <c r="A354">
         <v>9331772</v>
       </c>
       <c r="B354" t="s">
-        <v>907</v>
+        <v>1109</v>
       </c>
       <c r="C354" t="s">
         <v>891</v>
@@ -7131,13 +7406,17 @@
       <c r="A355">
         <v>9331893</v>
       </c>
-      <c r="B355" s="6"/>
+      <c r="B355" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C355" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="356" spans="1:3">
       <c r="A356">
         <v>9331945</v>
       </c>
-      <c r="B356" s="6"/>
     </row>
     <row r="357" spans="1:3">
       <c r="A357">
@@ -7154,14 +7433,13 @@
       <c r="A358">
         <v>9332215</v>
       </c>
-      <c r="B358" s="6"/>
     </row>
     <row r="359" spans="1:3">
       <c r="A359">
         <v>9334487</v>
       </c>
       <c r="B359" t="s">
-        <v>935</v>
+        <v>1098</v>
       </c>
       <c r="C359" t="s">
         <v>891</v>
@@ -7182,20 +7460,18 @@
       <c r="A361">
         <v>9337077</v>
       </c>
-      <c r="B361" s="6"/>
     </row>
     <row r="362" spans="1:3">
       <c r="A362">
         <v>9337134</v>
       </c>
-      <c r="B362" s="6"/>
     </row>
     <row r="363" spans="1:3">
       <c r="A363">
         <v>9337179</v>
       </c>
-      <c r="B363" s="4" t="s">
-        <v>936</v>
+      <c r="B363" t="s">
+        <v>920</v>
       </c>
       <c r="C363" t="s">
         <v>899</v>
@@ -7205,13 +7481,11 @@
       <c r="A364">
         <v>9337290</v>
       </c>
-      <c r="B364" s="6"/>
     </row>
     <row r="365" spans="1:3">
       <c r="A365">
         <v>9337292</v>
       </c>
-      <c r="B365" s="6"/>
     </row>
     <row r="366" spans="1:3">
       <c r="A366">
@@ -7233,7 +7507,7 @@
       <c r="A368">
         <v>9337382</v>
       </c>
-      <c r="B368" s="2" t="s">
+      <c r="B368" t="s">
         <v>612</v>
       </c>
       <c r="C368" t="s">
@@ -7244,14 +7518,13 @@
       <c r="A369">
         <v>9337465</v>
       </c>
-      <c r="B369" s="6"/>
     </row>
     <row r="370" spans="1:3">
       <c r="A370">
         <v>9337474</v>
       </c>
       <c r="B370" t="s">
-        <v>937</v>
+        <v>921</v>
       </c>
       <c r="C370" t="s">
         <v>897</v>
@@ -7261,14 +7534,13 @@
       <c r="A371">
         <v>9337479</v>
       </c>
-      <c r="B371" s="6"/>
     </row>
     <row r="372" spans="1:3">
       <c r="A372">
         <v>9337559</v>
       </c>
       <c r="B372" t="s">
-        <v>938</v>
+        <v>922</v>
       </c>
       <c r="C372" t="s">
         <v>891</v>
@@ -7299,7 +7571,6 @@
       <c r="A376">
         <v>9340305</v>
       </c>
-      <c r="B376" s="6"/>
     </row>
     <row r="377" spans="1:3">
       <c r="A377">
@@ -7317,7 +7588,7 @@
         <v>9340397</v>
       </c>
       <c r="B378" t="s">
-        <v>939</v>
+        <v>923</v>
       </c>
       <c r="C378" t="s">
         <v>892</v>
@@ -7327,8 +7598,8 @@
       <c r="A379">
         <v>9340398</v>
       </c>
-      <c r="B379" s="4" t="s">
-        <v>940</v>
+      <c r="B379" t="s">
+        <v>924</v>
       </c>
       <c r="C379" t="s">
         <v>892</v>
@@ -7349,13 +7620,23 @@
       <c r="A381">
         <v>9340404</v>
       </c>
-      <c r="B381" s="6"/>
+      <c r="B381" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C381" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="382" spans="1:3">
       <c r="A382">
         <v>9340407</v>
       </c>
-      <c r="B382" s="6"/>
+      <c r="B382" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C382" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383">
@@ -7377,14 +7658,13 @@
       <c r="A385">
         <v>9340508</v>
       </c>
-      <c r="B385" s="6"/>
     </row>
     <row r="386" spans="1:3">
       <c r="A386">
         <v>9340584</v>
       </c>
       <c r="B386" t="s">
-        <v>941</v>
+        <v>925</v>
       </c>
       <c r="C386" t="s">
         <v>899</v>
@@ -7449,8 +7729,8 @@
       <c r="A392">
         <v>9341277</v>
       </c>
-      <c r="B392" s="4" t="s">
-        <v>942</v>
+      <c r="B392" t="s">
+        <v>926</v>
       </c>
       <c r="C392" t="s">
         <v>891</v>
@@ -7492,8 +7772,8 @@
       <c r="A397">
         <v>9341441</v>
       </c>
-      <c r="B397" s="4" t="s">
-        <v>943</v>
+      <c r="B397" t="s">
+        <v>927</v>
       </c>
       <c r="C397" t="s">
         <v>899</v>
@@ -7519,7 +7799,6 @@
       <c r="A400">
         <v>9341596</v>
       </c>
-      <c r="B400" s="6"/>
     </row>
     <row r="401" spans="1:3">
       <c r="A401">
@@ -7531,7 +7810,7 @@
         <v>9341692</v>
       </c>
       <c r="B402" t="s">
-        <v>944</v>
+        <v>928</v>
       </c>
       <c r="C402" t="s">
         <v>897</v>
@@ -7542,7 +7821,7 @@
         <v>9341693</v>
       </c>
       <c r="B403" t="s">
-        <v>945</v>
+        <v>929</v>
       </c>
       <c r="C403" t="s">
         <v>897</v>
@@ -7564,7 +7843,7 @@
         <v>9341862</v>
       </c>
       <c r="B405" t="s">
-        <v>946</v>
+        <v>1107</v>
       </c>
       <c r="C405" t="s">
         <v>891</v>
@@ -7575,7 +7854,7 @@
         <v>9341893</v>
       </c>
       <c r="B406" t="s">
-        <v>947</v>
+        <v>930</v>
       </c>
       <c r="C406" t="s">
         <v>899</v>
@@ -7585,8 +7864,8 @@
       <c r="A407">
         <v>9342061</v>
       </c>
-      <c r="B407" s="4" t="s">
-        <v>948</v>
+      <c r="B407" t="s">
+        <v>931</v>
       </c>
       <c r="C407" t="s">
         <v>891</v>
@@ -7629,8 +7908,8 @@
       <c r="A411">
         <v>9342926</v>
       </c>
-      <c r="B411" s="4" t="s">
-        <v>949</v>
+      <c r="B411" t="s">
+        <v>1046</v>
       </c>
       <c r="C411" t="s">
         <v>891</v>
@@ -7640,19 +7919,24 @@
       <c r="A412">
         <v>9342938</v>
       </c>
+      <c r="B412" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C412" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="413" spans="1:3">
       <c r="A413">
         <v>9342941</v>
       </c>
-      <c r="B413" s="5"/>
     </row>
     <row r="414" spans="1:3">
       <c r="A414">
         <v>9344011</v>
       </c>
-      <c r="B414" s="4" t="s">
-        <v>950</v>
+      <c r="B414" t="s">
+        <v>932</v>
       </c>
       <c r="C414" t="s">
         <v>899</v>
@@ -7777,8 +8061,8 @@
       <c r="A426">
         <v>9344201</v>
       </c>
-      <c r="B426" s="4" t="s">
-        <v>951</v>
+      <c r="B426" t="s">
+        <v>933</v>
       </c>
       <c r="C426" t="s">
         <v>897</v>
@@ -7799,11 +8083,23 @@
       <c r="A428">
         <v>9344208</v>
       </c>
+      <c r="B428" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C428" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="429" spans="1:3">
       <c r="A429">
         <v>9344495</v>
       </c>
+      <c r="B429" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C429" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="430" spans="1:3">
       <c r="A430">
@@ -7831,6 +8127,12 @@
       <c r="A432">
         <v>9344681</v>
       </c>
+      <c r="B432" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C432" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="433" spans="1:3">
       <c r="A433">
@@ -7924,6 +8226,12 @@
       <c r="A441">
         <v>9345086</v>
       </c>
+      <c r="B441" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C441" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="442" spans="1:3">
       <c r="A442">
@@ -7973,6 +8281,12 @@
       <c r="A446">
         <v>9345153</v>
       </c>
+      <c r="B446" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C446" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="447" spans="1:3">
       <c r="A447">
@@ -8044,8 +8358,8 @@
       <c r="A453">
         <v>9345638</v>
       </c>
-      <c r="B453" s="4" t="s">
-        <v>952</v>
+      <c r="B453" t="s">
+        <v>934</v>
       </c>
       <c r="C453" t="s">
         <v>893</v>
@@ -8055,8 +8369,8 @@
       <c r="A454">
         <v>9345692</v>
       </c>
-      <c r="B454" s="4" t="s">
-        <v>953</v>
+      <c r="B454" t="s">
+        <v>1058</v>
       </c>
       <c r="C454" t="s">
         <v>891</v>
@@ -8082,8 +8396,8 @@
       <c r="A457">
         <v>9345896</v>
       </c>
-      <c r="B457" s="4" t="s">
-        <v>954</v>
+      <c r="B457" t="s">
+        <v>935</v>
       </c>
       <c r="C457" t="s">
         <v>891</v>
@@ -8093,8 +8407,8 @@
       <c r="A458">
         <v>9345938</v>
       </c>
-      <c r="B458" s="4" t="s">
-        <v>955</v>
+      <c r="B458" t="s">
+        <v>1047</v>
       </c>
       <c r="C458" t="s">
         <v>891</v>
@@ -8104,8 +8418,8 @@
       <c r="A459">
         <v>9345943</v>
       </c>
-      <c r="B459" s="4" t="s">
-        <v>956</v>
+      <c r="B459" t="s">
+        <v>1054</v>
       </c>
       <c r="C459" t="s">
         <v>891</v>
@@ -8115,18 +8429,30 @@
       <c r="A460">
         <v>9345968</v>
       </c>
+      <c r="B460" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C460" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="461" spans="1:3">
       <c r="A461">
         <v>9345969</v>
       </c>
+      <c r="B461" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C461" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="462" spans="1:3">
       <c r="A462">
         <v>9346016</v>
       </c>
-      <c r="B462" s="4" t="s">
-        <v>957</v>
+      <c r="B462" t="s">
+        <v>1041</v>
       </c>
       <c r="C462" t="s">
         <v>891</v>
@@ -8152,25 +8478,21 @@
       <c r="A465">
         <v>9346053</v>
       </c>
-      <c r="B465" s="6"/>
     </row>
     <row r="466" spans="1:3">
       <c r="A466">
         <v>9346054</v>
       </c>
-      <c r="B466" s="6"/>
     </row>
     <row r="467" spans="1:3">
       <c r="A467">
         <v>9346055</v>
       </c>
-      <c r="B467" s="6"/>
     </row>
     <row r="468" spans="1:3">
       <c r="A468">
         <v>9346056</v>
       </c>
-      <c r="B468" s="6"/>
     </row>
     <row r="469" spans="1:3">
       <c r="A469">
@@ -8220,20 +8542,18 @@
       <c r="A473">
         <v>9346289</v>
       </c>
-      <c r="B473" s="6"/>
     </row>
     <row r="474" spans="1:3">
       <c r="A474">
         <v>9346290</v>
       </c>
-      <c r="B474" s="6"/>
     </row>
     <row r="475" spans="1:3">
       <c r="A475">
         <v>9346352</v>
       </c>
-      <c r="B475" s="4" t="s">
-        <v>958</v>
+      <c r="B475" t="s">
+        <v>936</v>
       </c>
       <c r="C475" t="s">
         <v>891</v>
@@ -8265,14 +8585,13 @@
       <c r="A478">
         <v>9346612</v>
       </c>
-      <c r="B478" s="6"/>
     </row>
     <row r="479" spans="1:3">
       <c r="A479">
         <v>9346613</v>
       </c>
-      <c r="B479" s="4" t="s">
-        <v>959</v>
+      <c r="B479" t="s">
+        <v>937</v>
       </c>
       <c r="C479" t="s">
         <v>891</v>
@@ -8293,8 +8612,8 @@
       <c r="A481">
         <v>9348572</v>
       </c>
-      <c r="B481" s="4" t="s">
-        <v>960</v>
+      <c r="B481" t="s">
+        <v>938</v>
       </c>
       <c r="C481" t="s">
         <v>891</v>
@@ -8304,8 +8623,8 @@
       <c r="A482">
         <v>9348750</v>
       </c>
-      <c r="B482" s="4" t="s">
-        <v>961</v>
+      <c r="B482" t="s">
+        <v>1060</v>
       </c>
       <c r="C482" t="s">
         <v>891</v>
@@ -8315,7 +8634,12 @@
       <c r="A483">
         <v>9348751</v>
       </c>
-      <c r="B483" s="6"/>
+      <c r="B483" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C483" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="484" spans="1:3">
       <c r="A484">
@@ -8365,11 +8689,11 @@
       <c r="A488">
         <v>9349514</v>
       </c>
-      <c r="B488" s="4" t="s">
-        <v>962</v>
+      <c r="B488" t="s">
+        <v>1059</v>
       </c>
       <c r="C488" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
     </row>
     <row r="489" spans="1:3">
@@ -8431,7 +8755,6 @@
       <c r="A494">
         <v>9360168</v>
       </c>
-      <c r="B494" s="6"/>
     </row>
     <row r="495" spans="1:3">
       <c r="A495">
@@ -8459,8 +8782,8 @@
       <c r="A497">
         <v>9361852</v>
       </c>
-      <c r="B497" s="4" t="s">
-        <v>963</v>
+      <c r="B497" t="s">
+        <v>1057</v>
       </c>
       <c r="C497" t="s">
         <v>891</v>
@@ -8470,7 +8793,12 @@
       <c r="A498">
         <v>9361856</v>
       </c>
-      <c r="B498" s="6"/>
+      <c r="B498" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C498" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="499" spans="1:3">
       <c r="A499">
@@ -8498,8 +8826,8 @@
       <c r="A501">
         <v>9363287</v>
       </c>
-      <c r="B501" s="4" t="s">
-        <v>964</v>
+      <c r="B501" t="s">
+        <v>939</v>
       </c>
       <c r="C501" t="s">
         <v>897</v>
@@ -8531,13 +8859,11 @@
       <c r="A504">
         <v>9368830</v>
       </c>
-      <c r="B504" s="6"/>
     </row>
     <row r="505" spans="1:3">
       <c r="A505">
         <v>9368832</v>
       </c>
-      <c r="B505" s="6"/>
     </row>
     <row r="506" spans="1:3">
       <c r="A506">
@@ -8587,8 +8913,8 @@
       <c r="A510">
         <v>9369193</v>
       </c>
-      <c r="B510" s="4" t="s">
-        <v>965</v>
+      <c r="B510" t="s">
+        <v>940</v>
       </c>
       <c r="C510" t="s">
         <v>891</v>
@@ -8686,8 +9012,8 @@
       <c r="A519">
         <v>9370625</v>
       </c>
-      <c r="B519" s="4" t="s">
-        <v>966</v>
+      <c r="B519" t="s">
+        <v>1115</v>
       </c>
       <c r="C519" t="s">
         <v>891</v>
@@ -8719,14 +9045,13 @@
       <c r="A522">
         <v>9370880</v>
       </c>
-      <c r="B522" s="6"/>
     </row>
     <row r="523" spans="1:3">
       <c r="A523">
         <v>9370889</v>
       </c>
-      <c r="B523" s="4" t="s">
-        <v>967</v>
+      <c r="B523" t="s">
+        <v>941</v>
       </c>
       <c r="C523" t="s">
         <v>896</v>
@@ -8736,14 +9061,13 @@
       <c r="A524">
         <v>9370954</v>
       </c>
-      <c r="B524" s="6"/>
     </row>
     <row r="525" spans="1:3">
       <c r="A525">
         <v>9370956</v>
       </c>
       <c r="B525" t="s">
-        <v>968</v>
+        <v>942</v>
       </c>
       <c r="C525" t="s">
         <v>891</v>
@@ -8753,8 +9077,8 @@
       <c r="A526">
         <v>9371449</v>
       </c>
-      <c r="B526" s="4" t="s">
-        <v>969</v>
+      <c r="B526" t="s">
+        <v>943</v>
       </c>
       <c r="C526" t="s">
         <v>891</v>
@@ -8775,8 +9099,8 @@
       <c r="A528">
         <v>9371937</v>
       </c>
-      <c r="B528" s="4" t="s">
-        <v>970</v>
+      <c r="B528" t="s">
+        <v>1038</v>
       </c>
       <c r="C528" t="s">
         <v>891</v>
@@ -8786,14 +9110,13 @@
       <c r="A529">
         <v>9372068</v>
       </c>
-      <c r="B529" s="6"/>
     </row>
     <row r="530" spans="1:3">
       <c r="A530">
         <v>9372086</v>
       </c>
-      <c r="B530" s="4" t="s">
-        <v>971</v>
+      <c r="B530" t="s">
+        <v>1081</v>
       </c>
       <c r="C530" t="s">
         <v>891</v>
@@ -8847,11 +9170,11 @@
       <c r="A535">
         <v>9372110</v>
       </c>
-      <c r="B535" s="4" t="s">
-        <v>972</v>
+      <c r="B535" t="s">
+        <v>1077</v>
       </c>
       <c r="C535" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
     </row>
     <row r="536" spans="1:3">
@@ -8890,8 +9213,8 @@
       <c r="A540">
         <v>9372387</v>
       </c>
-      <c r="B540" s="4" t="s">
-        <v>973</v>
+      <c r="B540" t="s">
+        <v>1082</v>
       </c>
       <c r="C540" t="s">
         <v>891</v>
@@ -8923,7 +9246,6 @@
       <c r="A543">
         <v>9372560</v>
       </c>
-      <c r="B543" s="6"/>
     </row>
     <row r="544" spans="1:3">
       <c r="A544">
@@ -8940,8 +9262,8 @@
       <c r="A545">
         <v>9372593</v>
       </c>
-      <c r="B545" s="4" t="s">
-        <v>974</v>
+      <c r="B545" t="s">
+        <v>944</v>
       </c>
       <c r="C545" t="s">
         <v>891</v>
@@ -8951,8 +9273,8 @@
       <c r="A546">
         <v>9372618</v>
       </c>
-      <c r="B546" s="4" t="s">
-        <v>975</v>
+      <c r="B546" t="s">
+        <v>945</v>
       </c>
       <c r="C546" t="s">
         <v>897</v>
@@ -8962,8 +9284,8 @@
       <c r="A547">
         <v>9372619</v>
       </c>
-      <c r="B547" s="4" t="s">
-        <v>976</v>
+      <c r="B547" t="s">
+        <v>946</v>
       </c>
       <c r="C547" t="s">
         <v>897</v>
@@ -8995,7 +9317,6 @@
       <c r="A550">
         <v>9372705</v>
       </c>
-      <c r="B550" s="6"/>
     </row>
     <row r="551" spans="1:3">
       <c r="A551">
@@ -9012,8 +9333,8 @@
       <c r="A552">
         <v>9372713</v>
       </c>
-      <c r="B552" s="4" t="s">
-        <v>977</v>
+      <c r="B552" t="s">
+        <v>947</v>
       </c>
       <c r="C552" t="s">
         <v>891</v>
@@ -9023,8 +9344,8 @@
       <c r="A553">
         <v>9372838</v>
       </c>
-      <c r="B553" s="4" t="s">
-        <v>978</v>
+      <c r="B553" t="s">
+        <v>1079</v>
       </c>
       <c r="C553" t="s">
         <v>891</v>
@@ -9056,7 +9377,12 @@
       <c r="A556">
         <v>9376506</v>
       </c>
-      <c r="B556" s="6"/>
+      <c r="B556" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C556" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="557" spans="1:3">
       <c r="A557">
@@ -9084,14 +9410,13 @@
       <c r="A559">
         <v>9379469</v>
       </c>
-      <c r="B559" s="6"/>
     </row>
     <row r="560" spans="1:3">
       <c r="A560">
         <v>9380051</v>
       </c>
-      <c r="B560" s="4" t="s">
-        <v>979</v>
+      <c r="B560" t="s">
+        <v>948</v>
       </c>
       <c r="C560" t="s">
         <v>891</v>
@@ -9123,8 +9448,8 @@
       <c r="A563">
         <v>9383435</v>
       </c>
-      <c r="B563" s="4" t="s">
-        <v>980</v>
+      <c r="B563" t="s">
+        <v>949</v>
       </c>
       <c r="C563" t="s">
         <v>896</v>
@@ -9145,14 +9470,13 @@
       <c r="A565">
         <v>9385639</v>
       </c>
-      <c r="B565" s="6"/>
     </row>
     <row r="566" spans="1:3">
       <c r="A566">
         <v>9385737</v>
       </c>
-      <c r="B566" s="4" t="s">
-        <v>981</v>
+      <c r="B566" t="s">
+        <v>950</v>
       </c>
       <c r="C566" t="s">
         <v>891</v>
@@ -9189,8 +9513,8 @@
       <c r="A570">
         <v>9386256</v>
       </c>
-      <c r="B570" s="4" t="s">
-        <v>982</v>
+      <c r="B570" t="s">
+        <v>1111</v>
       </c>
       <c r="C570" t="s">
         <v>891</v>
@@ -9205,6 +9529,12 @@
       <c r="A572">
         <v>9387983</v>
       </c>
+      <c r="B572" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C572" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="573" spans="1:3">
       <c r="A573">
@@ -9221,14 +9551,13 @@
       <c r="A574">
         <v>9388864</v>
       </c>
-      <c r="B574" s="6"/>
     </row>
     <row r="575" spans="1:3">
       <c r="A575">
         <v>9388879</v>
       </c>
-      <c r="B575" s="4" t="s">
-        <v>983</v>
+      <c r="B575" t="s">
+        <v>951</v>
       </c>
       <c r="C575" t="s">
         <v>891</v>
@@ -9238,8 +9567,8 @@
       <c r="A576">
         <v>9389062</v>
       </c>
-      <c r="B576" s="4" t="s">
-        <v>984</v>
+      <c r="B576" t="s">
+        <v>952</v>
       </c>
       <c r="C576" t="s">
         <v>897</v>
@@ -9260,8 +9589,8 @@
       <c r="A578">
         <v>9389384</v>
       </c>
-      <c r="B578" s="4" t="s">
-        <v>985</v>
+      <c r="B578" t="s">
+        <v>953</v>
       </c>
       <c r="C578" t="s">
         <v>897</v>
@@ -9870,7 +10199,6 @@
       <c r="A634">
         <v>9397805</v>
       </c>
-      <c r="B634" s="6"/>
     </row>
     <row r="635" spans="1:3">
       <c r="A635">
@@ -9997,7 +10325,6 @@
       <c r="A646">
         <v>9402788</v>
       </c>
-      <c r="B646" s="6"/>
     </row>
     <row r="647" spans="1:3">
       <c r="A647">
@@ -10062,7 +10389,6 @@
       <c r="A654">
         <v>9403769</v>
       </c>
-      <c r="B654" s="6"/>
     </row>
     <row r="655" spans="1:3">
       <c r="A655">
@@ -10145,7 +10471,6 @@
       <c r="A662">
         <v>9405401</v>
       </c>
-      <c r="B662" s="6"/>
     </row>
     <row r="663" spans="1:3">
       <c r="A663">
@@ -10173,7 +10498,6 @@
       <c r="A665">
         <v>9405408</v>
       </c>
-      <c r="B665" s="6"/>
     </row>
     <row r="666" spans="1:3">
       <c r="A666">
@@ -10268,7 +10592,7 @@
         <v>9406386</v>
       </c>
       <c r="B674" t="s">
-        <v>986</v>
+        <v>954</v>
       </c>
       <c r="C674" t="s">
         <v>892</v>
@@ -10279,7 +10603,7 @@
         <v>9406387</v>
       </c>
       <c r="B675" t="s">
-        <v>986</v>
+        <v>954</v>
       </c>
       <c r="C675" t="s">
         <v>892</v>
@@ -10290,7 +10614,7 @@
         <v>9406388</v>
       </c>
       <c r="B676" t="s">
-        <v>986</v>
+        <v>954</v>
       </c>
       <c r="C676" t="s">
         <v>892</v>
@@ -10301,7 +10625,7 @@
         <v>9406391</v>
       </c>
       <c r="B677" t="s">
-        <v>986</v>
+        <v>954</v>
       </c>
       <c r="C677" t="s">
         <v>892</v>
@@ -10312,7 +10636,7 @@
         <v>9406393</v>
       </c>
       <c r="B678" t="s">
-        <v>986</v>
+        <v>954</v>
       </c>
       <c r="C678" t="s">
         <v>892</v>
@@ -10323,7 +10647,7 @@
         <v>9406395</v>
       </c>
       <c r="B679" t="s">
-        <v>987</v>
+        <v>955</v>
       </c>
       <c r="C679" t="s">
         <v>892</v>
@@ -10334,7 +10658,7 @@
         <v>9406398</v>
       </c>
       <c r="B680" t="s">
-        <v>986</v>
+        <v>954</v>
       </c>
       <c r="C680" t="s">
         <v>892</v>
@@ -10345,7 +10669,7 @@
         <v>9406399</v>
       </c>
       <c r="B681" t="s">
-        <v>986</v>
+        <v>954</v>
       </c>
       <c r="C681" t="s">
         <v>892</v>
@@ -10443,7 +10767,6 @@
       <c r="A690">
         <v>9406906</v>
       </c>
-      <c r="B690" s="6"/>
     </row>
     <row r="691" spans="1:3">
       <c r="A691">
@@ -10614,7 +10937,6 @@
       <c r="A706">
         <v>9408248</v>
       </c>
-      <c r="B706" s="6"/>
     </row>
     <row r="707" spans="1:3">
       <c r="A707">
@@ -10862,32 +11184,52 @@
       <c r="A729">
         <v>9408843</v>
       </c>
-      <c r="B729" s="6"/>
+      <c r="B729" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C729" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="730" spans="1:3">
       <c r="A730">
         <v>9408844</v>
       </c>
-      <c r="B730" s="6"/>
+      <c r="B730" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C730" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="731" spans="1:3">
       <c r="A731">
         <v>9408845</v>
       </c>
-      <c r="B731" s="6"/>
+      <c r="B731" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C731" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="732" spans="1:3">
       <c r="A732">
         <v>9408846</v>
       </c>
-      <c r="B732" s="6"/>
+      <c r="B732" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C732" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="733" spans="1:3">
       <c r="A733">
         <v>9408847</v>
       </c>
-      <c r="B733" s="4" t="s">
-        <v>988</v>
+      <c r="B733" t="s">
+        <v>956</v>
       </c>
       <c r="C733" t="s">
         <v>891</v>
@@ -10908,8 +11250,8 @@
       <c r="A735">
         <v>9408849</v>
       </c>
-      <c r="B735" s="4" t="s">
-        <v>989</v>
+      <c r="B735" t="s">
+        <v>957</v>
       </c>
       <c r="C735" t="s">
         <v>891</v>
@@ -10963,8 +11305,8 @@
       <c r="A740">
         <v>9409752</v>
       </c>
-      <c r="B740" s="4" t="s">
-        <v>990</v>
+      <c r="B740" t="s">
+        <v>1116</v>
       </c>
       <c r="C740" t="s">
         <v>891</v>
@@ -11029,7 +11371,7 @@
       <c r="A746">
         <v>9410111</v>
       </c>
-      <c r="B746" s="6" t="s">
+      <c r="B746" t="s">
         <v>416</v>
       </c>
       <c r="C746" t="s">
@@ -11337,13 +11679,17 @@
       <c r="A774">
         <v>9415539</v>
       </c>
-      <c r="B774" s="6"/>
+      <c r="B774" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C774" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="775" spans="1:3">
       <c r="A775">
         <v>9415540</v>
       </c>
-      <c r="B775" s="6"/>
     </row>
     <row r="776" spans="1:3">
       <c r="A776">
@@ -11371,8 +11717,8 @@
       <c r="A778">
         <v>9417650</v>
       </c>
-      <c r="B778" s="4" t="s">
-        <v>991</v>
+      <c r="B778" t="s">
+        <v>958</v>
       </c>
       <c r="C778" t="s">
         <v>891</v>
@@ -11382,7 +11728,12 @@
       <c r="A779">
         <v>9417660</v>
       </c>
-      <c r="B779" s="6"/>
+      <c r="B779" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C779" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="780" spans="1:3">
       <c r="A780">
@@ -11421,13 +11772,17 @@
       <c r="A783">
         <v>9422069</v>
       </c>
-      <c r="B783" s="6"/>
+      <c r="B783" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C783" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="784" spans="1:3">
       <c r="A784">
         <v>9424308</v>
       </c>
-      <c r="B784" s="6"/>
     </row>
     <row r="785" spans="1:3">
       <c r="A785">
@@ -11444,8 +11799,8 @@
       <c r="A786">
         <v>9424609</v>
       </c>
-      <c r="B786" s="4" t="s">
-        <v>992</v>
+      <c r="B786" t="s">
+        <v>1085</v>
       </c>
       <c r="C786" t="s">
         <v>891</v>
@@ -11554,19 +11909,16 @@
       <c r="A796">
         <v>9428104</v>
       </c>
-      <c r="B796" s="6"/>
     </row>
     <row r="797" spans="1:3">
       <c r="A797">
         <v>9428110</v>
       </c>
-      <c r="B797" s="6"/>
     </row>
     <row r="798" spans="1:3">
       <c r="A798">
         <v>9428121</v>
       </c>
-      <c r="B798" s="6"/>
     </row>
     <row r="799" spans="1:3">
       <c r="A799">
@@ -11617,7 +11969,7 @@
         <v>9428343</v>
       </c>
       <c r="B803" t="s">
-        <v>993</v>
+        <v>959</v>
       </c>
       <c r="C803" t="s">
         <v>891</v>
@@ -11649,7 +12001,6 @@
       <c r="A806">
         <v>9429417</v>
       </c>
-      <c r="B806" s="6"/>
     </row>
     <row r="807" spans="1:3">
       <c r="A807">
@@ -11677,8 +12028,8 @@
       <c r="A809">
         <v>9430577</v>
       </c>
-      <c r="B809" s="6" t="s">
-        <v>994</v>
+      <c r="B809" t="s">
+        <v>960</v>
       </c>
       <c r="C809" t="s">
         <v>891</v>
@@ -11699,8 +12050,8 @@
       <c r="A811">
         <v>9430917</v>
       </c>
-      <c r="B811" s="4" t="s">
-        <v>995</v>
+      <c r="B811" t="s">
+        <v>961</v>
       </c>
       <c r="C811" t="s">
         <v>898</v>
@@ -11732,7 +12083,7 @@
       <c r="A814">
         <v>9433721</v>
       </c>
-      <c r="B814" s="2" t="s">
+      <c r="B814" t="s">
         <v>361</v>
       </c>
       <c r="C814" t="s">
@@ -11809,19 +12160,16 @@
       <c r="A821">
         <v>9433735</v>
       </c>
-      <c r="B821" s="6"/>
     </row>
     <row r="822" spans="1:3">
       <c r="A822">
         <v>9433736</v>
       </c>
-      <c r="B822" s="6"/>
     </row>
     <row r="823" spans="1:3">
       <c r="A823">
         <v>9433738</v>
       </c>
-      <c r="B823" s="6"/>
     </row>
     <row r="824" spans="1:3">
       <c r="A824">
@@ -11926,7 +12274,7 @@
       <c r="A833">
         <v>9436933</v>
       </c>
-      <c r="B833" s="2" t="s">
+      <c r="B833" t="s">
         <v>346</v>
       </c>
       <c r="C833" t="s">
@@ -12135,8 +12483,8 @@
       <c r="A852">
         <v>9439794</v>
       </c>
-      <c r="B852" s="4" t="s">
-        <v>996</v>
+      <c r="B852" t="s">
+        <v>1112</v>
       </c>
       <c r="C852" t="s">
         <v>891</v>
@@ -12257,7 +12605,7 @@
         <v>9441307</v>
       </c>
       <c r="B863" t="s">
-        <v>997</v>
+        <v>1051</v>
       </c>
       <c r="C863" t="s">
         <v>891</v>
@@ -12730,7 +13078,7 @@
         <v>9445734</v>
       </c>
       <c r="B906" t="s">
-        <v>1034</v>
+        <v>995</v>
       </c>
       <c r="C906" t="s">
         <v>892</v>
@@ -12796,7 +13144,7 @@
         <v>9445748</v>
       </c>
       <c r="B912" t="s">
-        <v>1033</v>
+        <v>994</v>
       </c>
       <c r="C912" t="s">
         <v>892</v>
@@ -12916,7 +13264,7 @@
       <c r="A923">
         <v>9445946</v>
       </c>
-      <c r="B923" s="2" t="s">
+      <c r="B923" t="s">
         <v>268</v>
       </c>
       <c r="C923" t="s">
@@ -13488,7 +13836,7 @@
       <c r="A975">
         <v>9454473</v>
       </c>
-      <c r="B975" s="2" t="s">
+      <c r="B975" t="s">
         <v>233</v>
       </c>
       <c r="C975" t="s">
@@ -13730,7 +14078,7 @@
       <c r="A997">
         <v>9456620</v>
       </c>
-      <c r="B997" s="2" t="s">
+      <c r="B997" t="s">
         <v>212</v>
       </c>
       <c r="C997" t="s">
@@ -13829,25 +14177,21 @@
       <c r="A1006">
         <v>9459042</v>
       </c>
-      <c r="B1006" s="6"/>
     </row>
     <row r="1007" spans="1:3">
       <c r="A1007">
         <v>9459044</v>
       </c>
-      <c r="B1007" s="6"/>
     </row>
     <row r="1008" spans="1:3">
       <c r="A1008">
         <v>9459045</v>
       </c>
-      <c r="B1008" s="6"/>
     </row>
     <row r="1009" spans="1:3">
       <c r="A1009">
         <v>9459047</v>
       </c>
-      <c r="B1009" s="6"/>
     </row>
     <row r="1010" spans="1:3">
       <c r="A1010">
@@ -13886,7 +14230,7 @@
       <c r="A1013">
         <v>9460000</v>
       </c>
-      <c r="B1013" s="2" t="s">
+      <c r="B1013" t="s">
         <v>201</v>
       </c>
       <c r="C1013" t="s">
@@ -13908,7 +14252,6 @@
       <c r="A1015">
         <v>9460025</v>
       </c>
-      <c r="B1015" s="6"/>
     </row>
     <row r="1016" spans="1:3">
       <c r="A1016">
@@ -13991,7 +14334,12 @@
       <c r="A1023">
         <v>9461431</v>
       </c>
-      <c r="B1023" s="6"/>
+      <c r="B1023" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C1023" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="1024" spans="1:3">
       <c r="A1024">
@@ -14008,23 +14356,40 @@
       <c r="A1025">
         <v>9461433</v>
       </c>
-      <c r="B1025" s="6"/>
+      <c r="B1025" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C1025" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="1026" spans="1:3">
       <c r="A1026">
         <v>9461434</v>
       </c>
+      <c r="B1026" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C1026" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="1027" spans="1:3">
       <c r="A1027">
         <v>9461435</v>
       </c>
+      <c r="B1027" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C1027" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="1028" spans="1:3">
       <c r="A1028">
         <v>9461437</v>
       </c>
-      <c r="B1028" s="5" t="s">
+      <c r="B1028" t="s">
         <v>858</v>
       </c>
       <c r="C1028" t="s">
@@ -14123,7 +14488,7 @@
       <c r="A1037">
         <v>9461451</v>
       </c>
-      <c r="B1037" s="6" t="s">
+      <c r="B1037" t="s">
         <v>866</v>
       </c>
       <c r="C1037" t="s">
@@ -14200,7 +14565,7 @@
       <c r="A1044">
         <v>9461461</v>
       </c>
-      <c r="B1044" s="6" t="s">
+      <c r="B1044" t="s">
         <v>871</v>
       </c>
       <c r="C1044" t="s">
@@ -14607,7 +14972,7 @@
       <c r="A1081">
         <v>9471872</v>
       </c>
-      <c r="B1081" s="5" t="s">
+      <c r="B1081" t="s">
         <v>159</v>
       </c>
       <c r="C1081" t="s">
@@ -14707,7 +15072,7 @@
         <v>9473323</v>
       </c>
       <c r="B1090" t="s">
-        <v>1032</v>
+        <v>993</v>
       </c>
       <c r="C1090" t="s">
         <v>891</v>
@@ -14728,8 +15093,8 @@
       <c r="A1092">
         <v>9473327</v>
       </c>
-      <c r="B1092" s="2" t="s">
-        <v>1028</v>
+      <c r="B1092" t="s">
+        <v>989</v>
       </c>
       <c r="C1092" t="s">
         <v>891</v>
@@ -14740,7 +15105,7 @@
         <v>9473328</v>
       </c>
       <c r="B1093" t="s">
-        <v>1031</v>
+        <v>992</v>
       </c>
       <c r="C1093" t="s">
         <v>891</v>
@@ -14751,7 +15116,7 @@
         <v>9473329</v>
       </c>
       <c r="B1094" t="s">
-        <v>1029</v>
+        <v>990</v>
       </c>
       <c r="C1094" t="s">
         <v>891</v>
@@ -14773,7 +15138,7 @@
         <v>9473439</v>
       </c>
       <c r="B1096" t="s">
-        <v>1027</v>
+        <v>988</v>
       </c>
       <c r="C1096" t="s">
         <v>891</v>
@@ -14788,14 +15153,13 @@
       <c r="A1098">
         <v>9473931</v>
       </c>
-      <c r="B1098" s="6"/>
     </row>
     <row r="1099" spans="1:3">
       <c r="A1099">
         <v>9473933</v>
       </c>
       <c r="B1099" t="s">
-        <v>1030</v>
+        <v>991</v>
       </c>
       <c r="C1099" t="s">
         <v>891</v>
@@ -14805,8 +15169,8 @@
       <c r="A1100">
         <v>9473934</v>
       </c>
-      <c r="B1100" s="6" t="s">
-        <v>998</v>
+      <c r="B1100" t="s">
+        <v>962</v>
       </c>
       <c r="C1100" t="s">
         <v>891</v>
@@ -14816,8 +15180,8 @@
       <c r="A1101">
         <v>9473935</v>
       </c>
-      <c r="B1101" s="4" t="s">
-        <v>999</v>
+      <c r="B1101" t="s">
+        <v>963</v>
       </c>
       <c r="C1101" t="s">
         <v>891</v>
@@ -14827,8 +15191,8 @@
       <c r="A1102">
         <v>9473937</v>
       </c>
-      <c r="B1102" s="4" t="s">
-        <v>1000</v>
+      <c r="B1102" t="s">
+        <v>964</v>
       </c>
       <c r="C1102" t="s">
         <v>891</v>
@@ -14838,8 +15202,8 @@
       <c r="A1103">
         <v>9473938</v>
       </c>
-      <c r="B1103" s="4" t="s">
-        <v>1001</v>
+      <c r="B1103" t="s">
+        <v>965</v>
       </c>
       <c r="C1103" t="s">
         <v>891</v>
@@ -14849,8 +15213,8 @@
       <c r="A1104">
         <v>9473939</v>
       </c>
-      <c r="B1104" s="4" t="s">
-        <v>1002</v>
+      <c r="B1104" t="s">
+        <v>966</v>
       </c>
       <c r="C1104" t="s">
         <v>891</v>
@@ -14860,8 +15224,8 @@
       <c r="A1105">
         <v>9473940</v>
       </c>
-      <c r="B1105" s="4" t="s">
-        <v>1003</v>
+      <c r="B1105" t="s">
+        <v>967</v>
       </c>
       <c r="C1105" t="s">
         <v>891</v>
@@ -14871,8 +15235,8 @@
       <c r="A1106">
         <v>9473941</v>
       </c>
-      <c r="B1106" s="4" t="s">
-        <v>1004</v>
+      <c r="B1106" t="s">
+        <v>968</v>
       </c>
       <c r="C1106" t="s">
         <v>891</v>
@@ -14882,8 +15246,8 @@
       <c r="A1107">
         <v>9473942</v>
       </c>
-      <c r="B1107" s="4" t="s">
-        <v>1005</v>
+      <c r="B1107" t="s">
+        <v>969</v>
       </c>
       <c r="C1107" t="s">
         <v>891</v>
@@ -14898,8 +15262,8 @@
       <c r="A1109">
         <v>9474023</v>
       </c>
-      <c r="B1109" s="4" t="s">
-        <v>1006</v>
+      <c r="B1109" t="s">
+        <v>970</v>
       </c>
       <c r="C1109" t="s">
         <v>891</v>
@@ -14909,8 +15273,8 @@
       <c r="A1110">
         <v>9474026</v>
       </c>
-      <c r="B1110" s="4" t="s">
-        <v>1007</v>
+      <c r="B1110" t="s">
+        <v>971</v>
       </c>
       <c r="C1110" t="s">
         <v>891</v>
@@ -14925,8 +15289,8 @@
       <c r="A1112">
         <v>9474077</v>
       </c>
-      <c r="B1112" s="4" t="s">
-        <v>1008</v>
+      <c r="B1112" t="s">
+        <v>972</v>
       </c>
       <c r="C1112" t="s">
         <v>891</v>
@@ -14936,8 +15300,8 @@
       <c r="A1113">
         <v>9474082</v>
       </c>
-      <c r="B1113" s="4" t="s">
-        <v>1009</v>
+      <c r="B1113" t="s">
+        <v>973</v>
       </c>
       <c r="C1113" t="s">
         <v>891</v>
@@ -14947,8 +15311,8 @@
       <c r="A1114">
         <v>9474088</v>
       </c>
-      <c r="B1114" s="4" t="s">
-        <v>1010</v>
+      <c r="B1114" t="s">
+        <v>974</v>
       </c>
       <c r="C1114" t="s">
         <v>891</v>
@@ -15123,7 +15487,7 @@
       <c r="A1130">
         <v>9475338</v>
       </c>
-      <c r="B1130" s="7" t="s">
+      <c r="B1130" t="s">
         <v>136</v>
       </c>
       <c r="C1130" t="s">
@@ -15156,7 +15520,7 @@
       <c r="A1133">
         <v>9476441</v>
       </c>
-      <c r="B1133" s="5" t="s">
+      <c r="B1133" t="s">
         <v>133</v>
       </c>
       <c r="C1133" t="s">
@@ -15332,7 +15696,7 @@
       <c r="A1149">
         <v>9480797</v>
       </c>
-      <c r="B1149" s="5" t="s">
+      <c r="B1149" t="s">
         <v>118</v>
       </c>
       <c r="C1149" t="s">
@@ -15464,7 +15828,7 @@
       <c r="A1161">
         <v>9480920</v>
       </c>
-      <c r="B1161" s="5" t="s">
+      <c r="B1161" t="s">
         <v>107</v>
       </c>
       <c r="C1161" t="s">
@@ -15530,7 +15894,7 @@
       <c r="A1167">
         <v>9480958</v>
       </c>
-      <c r="B1167" s="5" t="s">
+      <c r="B1167" t="s">
         <v>101</v>
       </c>
       <c r="C1167" t="s">
@@ -15563,7 +15927,7 @@
       <c r="A1170">
         <v>9481011</v>
       </c>
-      <c r="B1170" s="5" t="s">
+      <c r="B1170" t="s">
         <v>98</v>
       </c>
       <c r="C1170" t="s">
@@ -15619,7 +15983,7 @@
         <v>9481081</v>
       </c>
       <c r="B1175" t="s">
-        <v>1025</v>
+        <v>986</v>
       </c>
       <c r="C1175" t="s">
         <v>892</v>
@@ -15640,7 +16004,7 @@
       <c r="A1177">
         <v>9481099</v>
       </c>
-      <c r="B1177" s="5" t="s">
+      <c r="B1177" t="s">
         <v>92</v>
       </c>
       <c r="C1177" t="s">
@@ -15651,7 +16015,7 @@
       <c r="A1178">
         <v>9481106</v>
       </c>
-      <c r="B1178" s="5" t="s">
+      <c r="B1178" t="s">
         <v>91</v>
       </c>
       <c r="C1178" t="s">
@@ -15684,7 +16048,7 @@
       <c r="A1181">
         <v>9481157</v>
       </c>
-      <c r="B1181" s="5" t="s">
+      <c r="B1181" t="s">
         <v>88</v>
       </c>
       <c r="C1181" t="s">
@@ -15706,7 +16070,7 @@
       <c r="A1183">
         <v>9481203</v>
       </c>
-      <c r="B1183" s="5" t="s">
+      <c r="B1183" t="s">
         <v>87</v>
       </c>
       <c r="C1183" t="s">
@@ -15772,7 +16136,7 @@
       <c r="A1189">
         <v>9481257</v>
       </c>
-      <c r="B1189" s="5" t="s">
+      <c r="B1189" t="s">
         <v>81</v>
       </c>
       <c r="C1189" t="s">
@@ -15783,7 +16147,7 @@
       <c r="A1190">
         <v>9481295</v>
       </c>
-      <c r="B1190" s="5" t="s">
+      <c r="B1190" t="s">
         <v>80</v>
       </c>
       <c r="C1190" t="s">
@@ -15805,7 +16169,7 @@
       <c r="A1192">
         <v>9481368</v>
       </c>
-      <c r="B1192" s="5" t="s">
+      <c r="B1192" t="s">
         <v>78</v>
       </c>
       <c r="C1192" t="s">
@@ -15816,8 +16180,8 @@
       <c r="A1193">
         <v>9481452</v>
       </c>
-      <c r="B1193" s="5" t="s">
-        <v>1024</v>
+      <c r="B1193" t="s">
+        <v>985</v>
       </c>
       <c r="C1193" t="s">
         <v>892</v>
@@ -15827,7 +16191,7 @@
       <c r="A1194">
         <v>9481458</v>
       </c>
-      <c r="B1194" s="5" t="s">
+      <c r="B1194" t="s">
         <v>77</v>
       </c>
       <c r="C1194" t="s">
@@ -15860,7 +16224,7 @@
       <c r="A1197">
         <v>9482078</v>
       </c>
-      <c r="B1197" s="5" t="s">
+      <c r="B1197" t="s">
         <v>74</v>
       </c>
       <c r="C1197" t="s">
@@ -15948,7 +16312,7 @@
       <c r="A1205">
         <v>9484244</v>
       </c>
-      <c r="B1205" s="5" t="s">
+      <c r="B1205" t="s">
         <v>66</v>
       </c>
       <c r="C1205" t="s">
@@ -15970,7 +16334,7 @@
       <c r="A1207">
         <v>9484454</v>
       </c>
-      <c r="B1207" s="5" t="s">
+      <c r="B1207" t="s">
         <v>64</v>
       </c>
       <c r="C1207" t="s">
@@ -15981,7 +16345,7 @@
       <c r="A1208">
         <v>9485429</v>
       </c>
-      <c r="B1208" s="5" t="s">
+      <c r="B1208" t="s">
         <v>704</v>
       </c>
       <c r="C1208" t="s">
@@ -15992,7 +16356,7 @@
       <c r="A1209">
         <v>9485645</v>
       </c>
-      <c r="B1209" s="5" t="s">
+      <c r="B1209" t="s">
         <v>63</v>
       </c>
       <c r="C1209" t="s">
@@ -16014,7 +16378,7 @@
       <c r="A1211">
         <v>9488033</v>
       </c>
-      <c r="B1211" s="5" t="s">
+      <c r="B1211" t="s">
         <v>61</v>
       </c>
       <c r="C1211" t="s">
@@ -16036,7 +16400,7 @@
       <c r="A1213">
         <v>9488829</v>
       </c>
-      <c r="B1213" s="5" t="s">
+      <c r="B1213" t="s">
         <v>434</v>
       </c>
       <c r="C1213" t="s">
@@ -16058,7 +16422,7 @@
       <c r="A1215">
         <v>9490297</v>
       </c>
-      <c r="B1215" s="5" t="s">
+      <c r="B1215" t="s">
         <v>703</v>
       </c>
       <c r="C1215" t="s">
@@ -16091,7 +16455,7 @@
       <c r="A1218">
         <v>9490508</v>
       </c>
-      <c r="B1218" s="5" t="s">
+      <c r="B1218" t="s">
         <v>186</v>
       </c>
       <c r="C1218" t="s">
@@ -16102,7 +16466,7 @@
       <c r="A1219">
         <v>9490675</v>
       </c>
-      <c r="B1219" s="5" t="s">
+      <c r="B1219" t="s">
         <v>55</v>
       </c>
       <c r="C1219" t="s">
@@ -16124,7 +16488,7 @@
       <c r="A1221">
         <v>9490683</v>
       </c>
-      <c r="B1221" s="5" t="s">
+      <c r="B1221" t="s">
         <v>889</v>
       </c>
       <c r="C1221" t="s">
@@ -16146,13 +16510,12 @@
       <c r="A1223">
         <v>9490809</v>
       </c>
-      <c r="B1223" s="6"/>
     </row>
     <row r="1224" spans="1:3">
       <c r="A1224">
         <v>9490938</v>
       </c>
-      <c r="B1224" s="5" t="s">
+      <c r="B1224" t="s">
         <v>52</v>
       </c>
       <c r="C1224" t="s">
@@ -16163,7 +16526,7 @@
       <c r="A1225">
         <v>9491792</v>
       </c>
-      <c r="B1225" s="5" t="s">
+      <c r="B1225" t="s">
         <v>704</v>
       </c>
       <c r="C1225" t="s">
@@ -16185,7 +16548,7 @@
       <c r="A1227">
         <v>9492077</v>
       </c>
-      <c r="B1227" s="5" t="s">
+      <c r="B1227" t="s">
         <v>49</v>
       </c>
       <c r="C1227" t="s">
@@ -16196,7 +16559,7 @@
       <c r="A1228">
         <v>9492079</v>
       </c>
-      <c r="B1228" s="5" t="s">
+      <c r="B1228" t="s">
         <v>48</v>
       </c>
       <c r="C1228" t="s">
@@ -16207,7 +16570,6 @@
       <c r="A1229">
         <v>9492098</v>
       </c>
-      <c r="B1229" s="6"/>
     </row>
     <row r="1230" spans="1:3">
       <c r="A1230">
@@ -16224,7 +16586,7 @@
       <c r="A1231">
         <v>9492477</v>
       </c>
-      <c r="B1231" s="5" t="s">
+      <c r="B1231" t="s">
         <v>45</v>
       </c>
       <c r="C1231" t="s">
@@ -16246,7 +16608,7 @@
       <c r="A1233">
         <v>9492881</v>
       </c>
-      <c r="B1233" s="5" t="s">
+      <c r="B1233" t="s">
         <v>43</v>
       </c>
       <c r="C1233" t="s">
@@ -16257,7 +16619,7 @@
       <c r="A1234">
         <v>9493230</v>
       </c>
-      <c r="B1234" s="5" t="s">
+      <c r="B1234" t="s">
         <v>42</v>
       </c>
       <c r="C1234" t="s">
@@ -16268,7 +16630,7 @@
       <c r="A1235">
         <v>9493233</v>
       </c>
-      <c r="B1235" s="5" t="s">
+      <c r="B1235" t="s">
         <v>167</v>
       </c>
       <c r="C1235" t="s">
@@ -16290,7 +16652,7 @@
       <c r="A1237">
         <v>9493538</v>
       </c>
-      <c r="B1237" s="5" t="s">
+      <c r="B1237" t="s">
         <v>39</v>
       </c>
       <c r="C1237" t="s">
@@ -16301,7 +16663,7 @@
       <c r="A1238">
         <v>9493539</v>
       </c>
-      <c r="B1238" s="5" t="s">
+      <c r="B1238" t="s">
         <v>38</v>
       </c>
       <c r="C1238" t="s">
@@ -16334,7 +16696,7 @@
       <c r="A1241">
         <v>9493542</v>
       </c>
-      <c r="B1241" s="5" t="s">
+      <c r="B1241" t="s">
         <v>35</v>
       </c>
       <c r="C1241" t="s">
@@ -16345,7 +16707,7 @@
       <c r="A1242">
         <v>9493543</v>
       </c>
-      <c r="B1242" s="5" t="s">
+      <c r="B1242" t="s">
         <v>34</v>
       </c>
       <c r="C1242" t="s">
@@ -16367,7 +16729,7 @@
       <c r="A1244">
         <v>9493545</v>
       </c>
-      <c r="B1244" s="5" t="s">
+      <c r="B1244" t="s">
         <v>830</v>
       </c>
       <c r="C1244" t="s">
@@ -16389,7 +16751,7 @@
       <c r="A1246">
         <v>9493592</v>
       </c>
-      <c r="B1246" s="5" t="s">
+      <c r="B1246" t="s">
         <v>32</v>
       </c>
       <c r="C1246" t="s">
@@ -16433,7 +16795,7 @@
       <c r="A1250">
         <v>9493598</v>
       </c>
-      <c r="B1250" s="5" t="s">
+      <c r="B1250" t="s">
         <v>163</v>
       </c>
       <c r="C1250" t="s">
@@ -16444,7 +16806,7 @@
       <c r="A1251">
         <v>9493599</v>
       </c>
-      <c r="B1251" s="5" t="s">
+      <c r="B1251" t="s">
         <v>165</v>
       </c>
       <c r="C1251" t="s">
@@ -16455,7 +16817,7 @@
       <c r="A1252">
         <v>9494482</v>
       </c>
-      <c r="B1252" s="5" t="s">
+      <c r="B1252" t="s">
         <v>829</v>
       </c>
       <c r="C1252" t="s">
@@ -16554,7 +16916,7 @@
       <c r="A1261">
         <v>9497029</v>
       </c>
-      <c r="B1261" s="2" t="s">
+      <c r="B1261" t="s">
         <v>25</v>
       </c>
       <c r="C1261" t="s">
@@ -16587,7 +16949,7 @@
       <c r="A1264">
         <v>9497436</v>
       </c>
-      <c r="B1264" s="6" t="s">
+      <c r="B1264" t="s">
         <v>23</v>
       </c>
       <c r="C1264" t="s">
@@ -16719,7 +17081,7 @@
       <c r="A1276">
         <v>9501834</v>
       </c>
-      <c r="B1276" s="5" t="s">
+      <c r="B1276" t="s">
         <v>12</v>
       </c>
       <c r="C1276" t="s">
@@ -16730,7 +17092,7 @@
       <c r="A1277">
         <v>9501835</v>
       </c>
-      <c r="B1277" s="5" t="s">
+      <c r="B1277" t="s">
         <v>11</v>
       </c>
       <c r="C1277" t="s">
@@ -16741,7 +17103,7 @@
       <c r="A1278">
         <v>9501837</v>
       </c>
-      <c r="B1278" s="5" t="s">
+      <c r="B1278" t="s">
         <v>59</v>
       </c>
       <c r="C1278" t="s">
@@ -16774,7 +17136,7 @@
       <c r="A1281">
         <v>9501917</v>
       </c>
-      <c r="B1281" s="5" t="s">
+      <c r="B1281" t="s">
         <v>886</v>
       </c>
       <c r="C1281" t="s">
@@ -16785,7 +17147,7 @@
       <c r="A1282">
         <v>9502113</v>
       </c>
-      <c r="B1282" s="6" t="s">
+      <c r="B1282" t="s">
         <v>8</v>
       </c>
       <c r="C1282" t="s">
@@ -16818,7 +17180,7 @@
       <c r="A1285">
         <v>9502684</v>
       </c>
-      <c r="B1285" s="5" t="s">
+      <c r="B1285" t="s">
         <v>5</v>
       </c>
       <c r="C1285" t="s">
@@ -16873,7 +17235,7 @@
       <c r="A1290">
         <v>9503547</v>
       </c>
-      <c r="B1290" s="6" t="s">
+      <c r="B1290" t="s">
         <v>0</v>
       </c>
       <c r="C1290" t="s">
@@ -16893,10 +17255,10 @@
     </row>
     <row r="1292" spans="1:3">
       <c r="A1292">
-        <v>9509659</v>
-      </c>
-      <c r="B1292" s="5" t="s">
-        <v>884</v>
+        <v>9506675</v>
+      </c>
+      <c r="B1292" t="s">
+        <v>1114</v>
       </c>
       <c r="C1292" t="s">
         <v>891</v>
@@ -16904,32 +17266,32 @@
     </row>
     <row r="1293" spans="1:3">
       <c r="A1293">
-        <v>9509673</v>
+        <v>9509659</v>
       </c>
       <c r="B1293" t="s">
-        <v>1011</v>
+        <v>884</v>
       </c>
       <c r="C1293" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
     </row>
     <row r="1294" spans="1:3">
       <c r="A1294">
-        <v>9509675</v>
-      </c>
-      <c r="B1294" s="4" t="s">
-        <v>1012</v>
+        <v>9509673</v>
+      </c>
+      <c r="B1294" t="s">
+        <v>975</v>
       </c>
       <c r="C1294" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
     </row>
     <row r="1295" spans="1:3">
       <c r="A1295">
-        <v>9509723</v>
-      </c>
-      <c r="B1295" s="4" t="s">
-        <v>1013</v>
+        <v>9509675</v>
+      </c>
+      <c r="B1295" t="s">
+        <v>976</v>
       </c>
       <c r="C1295" t="s">
         <v>891</v>
@@ -16937,10 +17299,10 @@
     </row>
     <row r="1296" spans="1:3">
       <c r="A1296">
-        <v>9509755</v>
-      </c>
-      <c r="B1296" s="5" t="s">
-        <v>885</v>
+        <v>9509723</v>
+      </c>
+      <c r="B1296" t="s">
+        <v>1102</v>
       </c>
       <c r="C1296" t="s">
         <v>891</v>
@@ -16948,10 +17310,10 @@
     </row>
     <row r="1297" spans="1:3">
       <c r="A1297">
-        <v>9509801</v>
+        <v>9509755</v>
       </c>
       <c r="B1297" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="C1297" t="s">
         <v>891</v>
@@ -16959,54 +17321,54 @@
     </row>
     <row r="1298" spans="1:3">
       <c r="A1298">
-        <v>9511190</v>
-      </c>
-      <c r="B1298" s="4" t="s">
-        <v>1014</v>
+        <v>9509801</v>
+      </c>
+      <c r="B1298" t="s">
+        <v>881</v>
       </c>
       <c r="C1298" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="1299" spans="1:3">
       <c r="A1299">
-        <v>9511662</v>
+        <v>9511190</v>
       </c>
       <c r="B1299" t="s">
-        <v>840</v>
+        <v>977</v>
       </c>
       <c r="C1299" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1300" spans="1:3">
       <c r="A1300">
-        <v>9511802</v>
-      </c>
-      <c r="B1300" s="4" t="s">
-        <v>1015</v>
+        <v>9511662</v>
+      </c>
+      <c r="B1300" t="s">
+        <v>840</v>
       </c>
       <c r="C1300" t="s">
-        <v>903</v>
+        <v>892</v>
       </c>
     </row>
     <row r="1301" spans="1:3">
       <c r="A1301">
-        <v>9511883</v>
+        <v>9511802</v>
       </c>
       <c r="B1301" t="s">
-        <v>832</v>
+        <v>978</v>
       </c>
       <c r="C1301" t="s">
-        <v>892</v>
+        <v>903</v>
       </c>
     </row>
     <row r="1302" spans="1:3">
       <c r="A1302">
-        <v>9511884</v>
+        <v>9511883</v>
       </c>
       <c r="B1302" t="s">
-        <v>842</v>
+        <v>832</v>
       </c>
       <c r="C1302" t="s">
         <v>892</v>
@@ -17014,7 +17376,7 @@
     </row>
     <row r="1303" spans="1:3">
       <c r="A1303">
-        <v>9511885</v>
+        <v>9511884</v>
       </c>
       <c r="B1303" t="s">
         <v>842</v>
@@ -17025,7 +17387,7 @@
     </row>
     <row r="1304" spans="1:3">
       <c r="A1304">
-        <v>9511886</v>
+        <v>9511885</v>
       </c>
       <c r="B1304" t="s">
         <v>842</v>
@@ -17036,10 +17398,10 @@
     </row>
     <row r="1305" spans="1:3">
       <c r="A1305">
-        <v>9511887</v>
+        <v>9511886</v>
       </c>
       <c r="B1305" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="C1305" t="s">
         <v>892</v>
@@ -17047,10 +17409,10 @@
     </row>
     <row r="1306" spans="1:3">
       <c r="A1306">
-        <v>9511888</v>
+        <v>9511887</v>
       </c>
       <c r="B1306" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="C1306" t="s">
         <v>892</v>
@@ -17058,10 +17420,10 @@
     </row>
     <row r="1307" spans="1:3">
       <c r="A1307">
-        <v>9511889</v>
+        <v>9511888</v>
       </c>
       <c r="B1307" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="C1307" t="s">
         <v>892</v>
@@ -17069,10 +17431,10 @@
     </row>
     <row r="1308" spans="1:3">
       <c r="A1308">
-        <v>9511890</v>
+        <v>9511889</v>
       </c>
       <c r="B1308" t="s">
-        <v>842</v>
+        <v>833</v>
       </c>
       <c r="C1308" t="s">
         <v>892</v>
@@ -17080,10 +17442,10 @@
     </row>
     <row r="1309" spans="1:3">
       <c r="A1309">
-        <v>9511891</v>
+        <v>9511890</v>
       </c>
       <c r="B1309" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="C1309" t="s">
         <v>892</v>
@@ -17091,10 +17453,10 @@
     </row>
     <row r="1310" spans="1:3">
       <c r="A1310">
-        <v>9511892</v>
-      </c>
-      <c r="B1310" s="5" t="s">
-        <v>833</v>
+        <v>9511891</v>
+      </c>
+      <c r="B1310" t="s">
+        <v>836</v>
       </c>
       <c r="C1310" t="s">
         <v>892</v>
@@ -17102,10 +17464,10 @@
     </row>
     <row r="1311" spans="1:3">
       <c r="A1311">
-        <v>9511893</v>
-      </c>
-      <c r="B1311" s="5" t="s">
-        <v>832</v>
+        <v>9511892</v>
+      </c>
+      <c r="B1311" t="s">
+        <v>833</v>
       </c>
       <c r="C1311" t="s">
         <v>892</v>
@@ -17113,10 +17475,10 @@
     </row>
     <row r="1312" spans="1:3">
       <c r="A1312">
-        <v>9511894</v>
-      </c>
-      <c r="B1312" s="5" t="s">
-        <v>841</v>
+        <v>9511893</v>
+      </c>
+      <c r="B1312" t="s">
+        <v>832</v>
       </c>
       <c r="C1312" t="s">
         <v>892</v>
@@ -17124,10 +17486,10 @@
     </row>
     <row r="1313" spans="1:3">
       <c r="A1313">
-        <v>9511896</v>
-      </c>
-      <c r="B1313" s="5" t="s">
-        <v>833</v>
+        <v>9511894</v>
+      </c>
+      <c r="B1313" t="s">
+        <v>841</v>
       </c>
       <c r="C1313" t="s">
         <v>892</v>
@@ -17135,9 +17497,9 @@
     </row>
     <row r="1314" spans="1:3">
       <c r="A1314">
-        <v>9511897</v>
-      </c>
-      <c r="B1314" s="5" t="s">
+        <v>9511896</v>
+      </c>
+      <c r="B1314" t="s">
         <v>833</v>
       </c>
       <c r="C1314" t="s">
@@ -17146,10 +17508,10 @@
     </row>
     <row r="1315" spans="1:3">
       <c r="A1315">
-        <v>9511921</v>
-      </c>
-      <c r="B1315" s="5" t="s">
-        <v>831</v>
+        <v>9511897</v>
+      </c>
+      <c r="B1315" t="s">
+        <v>833</v>
       </c>
       <c r="C1315" t="s">
         <v>892</v>
@@ -17157,10 +17519,10 @@
     </row>
     <row r="1316" spans="1:3">
       <c r="A1316">
-        <v>9511922</v>
-      </c>
-      <c r="B1316" s="5" t="s">
-        <v>837</v>
+        <v>9511921</v>
+      </c>
+      <c r="B1316" t="s">
+        <v>831</v>
       </c>
       <c r="C1316" t="s">
         <v>892</v>
@@ -17168,10 +17530,10 @@
     </row>
     <row r="1317" spans="1:3">
       <c r="A1317">
-        <v>9511924</v>
+        <v>9511922</v>
       </c>
       <c r="B1317" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C1317" t="s">
         <v>892</v>
@@ -17179,10 +17541,10 @@
     </row>
     <row r="1318" spans="1:3">
       <c r="A1318">
-        <v>9512004</v>
-      </c>
-      <c r="B1318" s="5" t="s">
-        <v>835</v>
+        <v>9511924</v>
+      </c>
+      <c r="B1318" t="s">
+        <v>839</v>
       </c>
       <c r="C1318" t="s">
         <v>892</v>
@@ -17190,10 +17552,10 @@
     </row>
     <row r="1319" spans="1:3">
       <c r="A1319">
-        <v>9512005</v>
-      </c>
-      <c r="B1319" s="5" t="s">
-        <v>834</v>
+        <v>9512004</v>
+      </c>
+      <c r="B1319" t="s">
+        <v>835</v>
       </c>
       <c r="C1319" t="s">
         <v>892</v>
@@ -17201,7 +17563,7 @@
     </row>
     <row r="1320" spans="1:3">
       <c r="A1320">
-        <v>9512010</v>
+        <v>9512005</v>
       </c>
       <c r="B1320" t="s">
         <v>834</v>
@@ -17212,9 +17574,9 @@
     </row>
     <row r="1321" spans="1:3">
       <c r="A1321">
-        <v>9512016</v>
-      </c>
-      <c r="B1321" s="5" t="s">
+        <v>9512010</v>
+      </c>
+      <c r="B1321" t="s">
         <v>834</v>
       </c>
       <c r="C1321" t="s">
@@ -17223,10 +17585,10 @@
     </row>
     <row r="1322" spans="1:3">
       <c r="A1322">
-        <v>9512021</v>
-      </c>
-      <c r="B1322" s="5" t="s">
-        <v>833</v>
+        <v>9512016</v>
+      </c>
+      <c r="B1322" t="s">
+        <v>834</v>
       </c>
       <c r="C1322" t="s">
         <v>892</v>
@@ -17234,9 +17596,9 @@
     </row>
     <row r="1323" spans="1:3">
       <c r="A1323">
-        <v>9512022</v>
-      </c>
-      <c r="B1323" s="5" t="s">
+        <v>9512021</v>
+      </c>
+      <c r="B1323" t="s">
         <v>833</v>
       </c>
       <c r="C1323" t="s">
@@ -17245,7 +17607,7 @@
     </row>
     <row r="1324" spans="1:3">
       <c r="A1324">
-        <v>9512023</v>
+        <v>9512022</v>
       </c>
       <c r="B1324" t="s">
         <v>833</v>
@@ -17256,7 +17618,7 @@
     </row>
     <row r="1325" spans="1:3">
       <c r="A1325">
-        <v>9512024</v>
+        <v>9512023</v>
       </c>
       <c r="B1325" t="s">
         <v>833</v>
@@ -17267,10 +17629,10 @@
     </row>
     <row r="1326" spans="1:3">
       <c r="A1326">
-        <v>9512335</v>
+        <v>9512024</v>
       </c>
       <c r="B1326" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="C1326" t="s">
         <v>892</v>
@@ -17278,10 +17640,10 @@
     </row>
     <row r="1327" spans="1:3">
       <c r="A1327">
-        <v>9512343</v>
-      </c>
-      <c r="B1327" s="5" t="s">
-        <v>1016</v>
+        <v>9512335</v>
+      </c>
+      <c r="B1327" t="s">
+        <v>838</v>
       </c>
       <c r="C1327" t="s">
         <v>892</v>
@@ -17289,10 +17651,10 @@
     </row>
     <row r="1328" spans="1:3">
       <c r="A1328">
-        <v>9512349</v>
-      </c>
-      <c r="B1328" s="5" t="s">
-        <v>1017</v>
+        <v>9512343</v>
+      </c>
+      <c r="B1328" t="s">
+        <v>979</v>
       </c>
       <c r="C1328" t="s">
         <v>892</v>
@@ -17300,10 +17662,10 @@
     </row>
     <row r="1329" spans="1:3">
       <c r="A1329">
-        <v>9512353</v>
-      </c>
-      <c r="B1329" s="5" t="s">
-        <v>1018</v>
+        <v>9512349</v>
+      </c>
+      <c r="B1329" t="s">
+        <v>980</v>
       </c>
       <c r="C1329" t="s">
         <v>892</v>
@@ -17311,10 +17673,10 @@
     </row>
     <row r="1330" spans="1:3">
       <c r="A1330">
-        <v>9512358</v>
-      </c>
-      <c r="B1330" s="5" t="s">
-        <v>1019</v>
+        <v>9512353</v>
+      </c>
+      <c r="B1330" t="s">
+        <v>981</v>
       </c>
       <c r="C1330" t="s">
         <v>892</v>
@@ -17322,10 +17684,10 @@
     </row>
     <row r="1331" spans="1:3">
       <c r="A1331">
-        <v>9512362</v>
+        <v>9512358</v>
       </c>
       <c r="B1331" t="s">
-        <v>1020</v>
+        <v>982</v>
       </c>
       <c r="C1331" t="s">
         <v>892</v>
@@ -17333,10 +17695,10 @@
     </row>
     <row r="1332" spans="1:3">
       <c r="A1332">
-        <v>9512396</v>
+        <v>9512362</v>
       </c>
       <c r="B1332" t="s">
-        <v>836</v>
+        <v>983</v>
       </c>
       <c r="C1332" t="s">
         <v>892</v>
@@ -17344,7 +17706,7 @@
     </row>
     <row r="1333" spans="1:3">
       <c r="A1333">
-        <v>9512455</v>
+        <v>9512396</v>
       </c>
       <c r="B1333" t="s">
         <v>836</v>
@@ -17355,7 +17717,7 @@
     </row>
     <row r="1334" spans="1:3">
       <c r="A1334">
-        <v>9512466</v>
+        <v>9512455</v>
       </c>
       <c r="B1334" t="s">
         <v>836</v>
@@ -17366,10 +17728,10 @@
     </row>
     <row r="1335" spans="1:3">
       <c r="A1335">
-        <v>9512481</v>
+        <v>9512466</v>
       </c>
       <c r="B1335" t="s">
-        <v>802</v>
+        <v>836</v>
       </c>
       <c r="C1335" t="s">
         <v>892</v>
@@ -17377,21 +17739,21 @@
     </row>
     <row r="1336" spans="1:3">
       <c r="A1336">
-        <v>9512487</v>
+        <v>9512481</v>
       </c>
       <c r="B1336" t="s">
-        <v>1021</v>
+        <v>802</v>
       </c>
       <c r="C1336" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="1337" spans="1:3">
       <c r="A1337">
-        <v>9512489</v>
-      </c>
-      <c r="B1337" s="3" t="s">
-        <v>1022</v>
+        <v>9512487</v>
+      </c>
+      <c r="B1337" t="s">
+        <v>1091</v>
       </c>
       <c r="C1337" t="s">
         <v>891</v>
@@ -17399,10 +17761,10 @@
     </row>
     <row r="1338" spans="1:3">
       <c r="A1338">
-        <v>9512569</v>
-      </c>
-      <c r="B1338" s="3" t="s">
-        <v>1023</v>
+        <v>9512489</v>
+      </c>
+      <c r="B1338" t="s">
+        <v>984</v>
       </c>
       <c r="C1338" t="s">
         <v>891</v>
@@ -17410,27 +17772,26 @@
     </row>
     <row r="1339" spans="1:3">
       <c r="A1339">
-        <v>9514985</v>
-      </c>
-      <c r="B1339" s="6"/>
+        <v>9512569</v>
+      </c>
+      <c r="B1339" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C1339" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="1340" spans="1:3">
       <c r="A1340">
-        <v>9515137</v>
-      </c>
-      <c r="B1340" s="6" t="s">
-        <v>1035</v>
-      </c>
-      <c r="C1340" t="s">
-        <v>891</v>
+        <v>9514985</v>
       </c>
     </row>
     <row r="1341" spans="1:3">
       <c r="A1341">
-        <v>9515642</v>
-      </c>
-      <c r="B1341" s="6" t="s">
-        <v>1036</v>
+        <v>9515137</v>
+      </c>
+      <c r="B1341" t="s">
+        <v>996</v>
       </c>
       <c r="C1341" t="s">
         <v>891</v>
@@ -17438,21 +17799,21 @@
     </row>
     <row r="1342" spans="1:3">
       <c r="A1342">
-        <v>9517418</v>
-      </c>
-      <c r="B1342" s="3" t="s">
-        <v>1037</v>
+        <v>9515642</v>
+      </c>
+      <c r="B1342" t="s">
+        <v>997</v>
       </c>
       <c r="C1342" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="1343" spans="1:3">
       <c r="A1343">
-        <v>9517421</v>
-      </c>
-      <c r="B1343" s="3" t="s">
-        <v>1038</v>
+        <v>9517418</v>
+      </c>
+      <c r="B1343" t="s">
+        <v>998</v>
       </c>
       <c r="C1343" t="s">
         <v>892</v>
@@ -17460,10 +17821,10 @@
     </row>
     <row r="1344" spans="1:3">
       <c r="A1344">
-        <v>9517422</v>
-      </c>
-      <c r="B1344" s="3" t="s">
-        <v>1039</v>
+        <v>9517421</v>
+      </c>
+      <c r="B1344" t="s">
+        <v>999</v>
       </c>
       <c r="C1344" t="s">
         <v>892</v>
@@ -17471,10 +17832,10 @@
     </row>
     <row r="1345" spans="1:3">
       <c r="A1345">
-        <v>9517423</v>
-      </c>
-      <c r="B1345" s="3" t="s">
-        <v>1040</v>
+        <v>9517422</v>
+      </c>
+      <c r="B1345" t="s">
+        <v>1000</v>
       </c>
       <c r="C1345" t="s">
         <v>892</v>
@@ -17482,10 +17843,10 @@
     </row>
     <row r="1346" spans="1:3">
       <c r="A1346">
-        <v>9517425</v>
-      </c>
-      <c r="B1346" s="3" t="s">
-        <v>1041</v>
+        <v>9517423</v>
+      </c>
+      <c r="B1346" t="s">
+        <v>1001</v>
       </c>
       <c r="C1346" t="s">
         <v>892</v>
@@ -17493,10 +17854,10 @@
     </row>
     <row r="1347" spans="1:3">
       <c r="A1347">
-        <v>9517433</v>
-      </c>
-      <c r="B1347" s="3" t="s">
-        <v>1042</v>
+        <v>9517425</v>
+      </c>
+      <c r="B1347" t="s">
+        <v>1002</v>
       </c>
       <c r="C1347" t="s">
         <v>892</v>
@@ -17504,10 +17865,10 @@
     </row>
     <row r="1348" spans="1:3">
       <c r="A1348">
-        <v>9517436</v>
-      </c>
-      <c r="B1348" s="3" t="s">
-        <v>1043</v>
+        <v>9517433</v>
+      </c>
+      <c r="B1348" t="s">
+        <v>1003</v>
       </c>
       <c r="C1348" t="s">
         <v>892</v>
@@ -17515,10 +17876,10 @@
     </row>
     <row r="1349" spans="1:3">
       <c r="A1349">
-        <v>9517441</v>
-      </c>
-      <c r="B1349" s="3" t="s">
-        <v>1044</v>
+        <v>9517436</v>
+      </c>
+      <c r="B1349" t="s">
+        <v>1004</v>
       </c>
       <c r="C1349" t="s">
         <v>892</v>
@@ -17526,10 +17887,10 @@
     </row>
     <row r="1350" spans="1:3">
       <c r="A1350">
-        <v>9517444</v>
-      </c>
-      <c r="B1350" s="3" t="s">
-        <v>1045</v>
+        <v>9517441</v>
+      </c>
+      <c r="B1350" t="s">
+        <v>1005</v>
       </c>
       <c r="C1350" t="s">
         <v>892</v>
@@ -17537,10 +17898,10 @@
     </row>
     <row r="1351" spans="1:3">
       <c r="A1351">
-        <v>9517450</v>
-      </c>
-      <c r="B1351" s="3" t="s">
-        <v>1046</v>
+        <v>9517444</v>
+      </c>
+      <c r="B1351" t="s">
+        <v>1006</v>
       </c>
       <c r="C1351" t="s">
         <v>892</v>
@@ -17548,10 +17909,10 @@
     </row>
     <row r="1352" spans="1:3">
       <c r="A1352">
-        <v>9517451</v>
-      </c>
-      <c r="B1352" s="3" t="s">
-        <v>1047</v>
+        <v>9517450</v>
+      </c>
+      <c r="B1352" t="s">
+        <v>1007</v>
       </c>
       <c r="C1352" t="s">
         <v>892</v>
@@ -17559,10 +17920,10 @@
     </row>
     <row r="1353" spans="1:3">
       <c r="A1353">
-        <v>9517453</v>
-      </c>
-      <c r="B1353" s="3" t="s">
-        <v>1048</v>
+        <v>9517451</v>
+      </c>
+      <c r="B1353" t="s">
+        <v>1008</v>
       </c>
       <c r="C1353" t="s">
         <v>892</v>
@@ -17570,10 +17931,10 @@
     </row>
     <row r="1354" spans="1:3">
       <c r="A1354">
-        <v>9517456</v>
-      </c>
-      <c r="B1354" s="3" t="s">
-        <v>1049</v>
+        <v>9517453</v>
+      </c>
+      <c r="B1354" t="s">
+        <v>1009</v>
       </c>
       <c r="C1354" t="s">
         <v>892</v>
@@ -17581,10 +17942,10 @@
     </row>
     <row r="1355" spans="1:3">
       <c r="A1355">
-        <v>9517468</v>
-      </c>
-      <c r="B1355" s="3" t="s">
-        <v>1050</v>
+        <v>9517456</v>
+      </c>
+      <c r="B1355" t="s">
+        <v>1010</v>
       </c>
       <c r="C1355" t="s">
         <v>892</v>
@@ -17592,10 +17953,10 @@
     </row>
     <row r="1356" spans="1:3">
       <c r="A1356">
-        <v>9517470</v>
-      </c>
-      <c r="B1356" s="3" t="s">
-        <v>1051</v>
+        <v>9517468</v>
+      </c>
+      <c r="B1356" t="s">
+        <v>1011</v>
       </c>
       <c r="C1356" t="s">
         <v>892</v>
@@ -17603,10 +17964,10 @@
     </row>
     <row r="1357" spans="1:3">
       <c r="A1357">
-        <v>9517478</v>
-      </c>
-      <c r="B1357" s="3" t="s">
-        <v>1052</v>
+        <v>9517470</v>
+      </c>
+      <c r="B1357" t="s">
+        <v>1012</v>
       </c>
       <c r="C1357" t="s">
         <v>892</v>
@@ -17614,10 +17975,10 @@
     </row>
     <row r="1358" spans="1:3">
       <c r="A1358">
-        <v>9517764</v>
-      </c>
-      <c r="B1358" s="3" t="s">
-        <v>1053</v>
+        <v>9517478</v>
+      </c>
+      <c r="B1358" t="s">
+        <v>1013</v>
       </c>
       <c r="C1358" t="s">
         <v>892</v>
@@ -17625,10 +17986,10 @@
     </row>
     <row r="1359" spans="1:3">
       <c r="A1359">
-        <v>9517774</v>
-      </c>
-      <c r="B1359" s="3" t="s">
-        <v>1054</v>
+        <v>9517764</v>
+      </c>
+      <c r="B1359" t="s">
+        <v>1014</v>
       </c>
       <c r="C1359" t="s">
         <v>892</v>
@@ -17636,10 +17997,10 @@
     </row>
     <row r="1360" spans="1:3">
       <c r="A1360">
-        <v>9517778</v>
-      </c>
-      <c r="B1360" s="3" t="s">
-        <v>1055</v>
+        <v>9517774</v>
+      </c>
+      <c r="B1360" t="s">
+        <v>1015</v>
       </c>
       <c r="C1360" t="s">
         <v>892</v>
@@ -17647,10 +18008,10 @@
     </row>
     <row r="1361" spans="1:3">
       <c r="A1361">
-        <v>9518360</v>
-      </c>
-      <c r="B1361" s="3" t="s">
-        <v>1056</v>
+        <v>9517778</v>
+      </c>
+      <c r="B1361" t="s">
+        <v>1016</v>
       </c>
       <c r="C1361" t="s">
         <v>892</v>
@@ -17658,10 +18019,10 @@
     </row>
     <row r="1362" spans="1:3">
       <c r="A1362">
-        <v>9518366</v>
-      </c>
-      <c r="B1362" s="3" t="s">
-        <v>1057</v>
+        <v>9518360</v>
+      </c>
+      <c r="B1362" t="s">
+        <v>1017</v>
       </c>
       <c r="C1362" t="s">
         <v>892</v>
@@ -17669,10 +18030,10 @@
     </row>
     <row r="1363" spans="1:3">
       <c r="A1363">
-        <v>9518369</v>
-      </c>
-      <c r="B1363" s="3" t="s">
-        <v>1058</v>
+        <v>9518366</v>
+      </c>
+      <c r="B1363" t="s">
+        <v>1018</v>
       </c>
       <c r="C1363" t="s">
         <v>892</v>
@@ -17680,10 +18041,10 @@
     </row>
     <row r="1364" spans="1:3">
       <c r="A1364">
-        <v>9518375</v>
-      </c>
-      <c r="B1364" s="3" t="s">
-        <v>1059</v>
+        <v>9518369</v>
+      </c>
+      <c r="B1364" t="s">
+        <v>1019</v>
       </c>
       <c r="C1364" t="s">
         <v>892</v>
@@ -17691,10 +18052,10 @@
     </row>
     <row r="1365" spans="1:3">
       <c r="A1365">
-        <v>9518379</v>
-      </c>
-      <c r="B1365" s="3" t="s">
-        <v>1060</v>
+        <v>9518375</v>
+      </c>
+      <c r="B1365" t="s">
+        <v>1020</v>
       </c>
       <c r="C1365" t="s">
         <v>892</v>
@@ -17702,10 +18063,10 @@
     </row>
     <row r="1366" spans="1:3">
       <c r="A1366">
-        <v>9518443</v>
-      </c>
-      <c r="B1366" s="3" t="s">
-        <v>1060</v>
+        <v>9518379</v>
+      </c>
+      <c r="B1366" t="s">
+        <v>1021</v>
       </c>
       <c r="C1366" t="s">
         <v>892</v>
@@ -17713,35 +18074,37 @@
     </row>
     <row r="1367" spans="1:3">
       <c r="A1367">
-        <v>9518724</v>
-      </c>
-      <c r="B1367" s="6" t="s">
-        <v>1061</v>
+        <v>9518443</v>
+      </c>
+      <c r="B1367" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C1367" t="s">
+        <v>892</v>
       </c>
     </row>
     <row r="1368" spans="1:3">
       <c r="A1368">
-        <v>9518769</v>
-      </c>
-      <c r="B1368" s="6"/>
+        <v>9518724</v>
+      </c>
+      <c r="B1368" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C1368" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="1369" spans="1:3">
       <c r="A1369">
-        <v>9518891</v>
-      </c>
-      <c r="B1369" s="3" t="s">
-        <v>1062</v>
-      </c>
-      <c r="C1369" t="s">
-        <v>891</v>
+        <v>9518769</v>
       </c>
     </row>
     <row r="1370" spans="1:3">
       <c r="A1370">
-        <v>9518926</v>
+        <v>9518891</v>
       </c>
       <c r="B1370" t="s">
-        <v>1063</v>
+        <v>1023</v>
       </c>
       <c r="C1370" t="s">
         <v>891</v>
@@ -17749,10 +18112,10 @@
     </row>
     <row r="1371" spans="1:3">
       <c r="A1371">
-        <v>9518927</v>
-      </c>
-      <c r="B1371" s="6" t="s">
-        <v>1064</v>
+        <v>9518926</v>
+      </c>
+      <c r="B1371" t="s">
+        <v>1024</v>
       </c>
       <c r="C1371" t="s">
         <v>891</v>
@@ -17760,10 +18123,10 @@
     </row>
     <row r="1372" spans="1:3">
       <c r="A1372">
-        <v>9518928</v>
+        <v>9518927</v>
       </c>
       <c r="B1372" t="s">
-        <v>1065</v>
+        <v>1025</v>
       </c>
       <c r="C1372" t="s">
         <v>891</v>
@@ -17771,10 +18134,10 @@
     </row>
     <row r="1373" spans="1:3">
       <c r="A1373">
-        <v>9518929</v>
-      </c>
-      <c r="B1373" s="3" t="s">
-        <v>1066</v>
+        <v>9518928</v>
+      </c>
+      <c r="B1373" t="s">
+        <v>1026</v>
       </c>
       <c r="C1373" t="s">
         <v>891</v>
@@ -17782,10 +18145,10 @@
     </row>
     <row r="1374" spans="1:3">
       <c r="A1374">
-        <v>9518930</v>
+        <v>9518929</v>
       </c>
       <c r="B1374" t="s">
-        <v>1067</v>
+        <v>1027</v>
       </c>
       <c r="C1374" t="s">
         <v>891</v>
@@ -17793,38 +18156,37 @@
     </row>
     <row r="1375" spans="1:3">
       <c r="A1375">
-        <v>9519023</v>
-      </c>
-      <c r="B1375" s="6"/>
+        <v>9518930</v>
+      </c>
+      <c r="B1375" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C1375" t="s">
+        <v>891</v>
+      </c>
     </row>
     <row r="1376" spans="1:3">
       <c r="A1376">
-        <v>9519027</v>
-      </c>
-      <c r="B1376" s="3" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C1376" t="s">
-        <v>893</v>
+        <v>9519023</v>
       </c>
     </row>
     <row r="1377" spans="1:3">
       <c r="A1377">
-        <v>9519031</v>
-      </c>
-      <c r="B1377" s="3" t="s">
-        <v>1069</v>
+        <v>9519027</v>
+      </c>
+      <c r="B1377" t="s">
+        <v>1029</v>
       </c>
       <c r="C1377" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1378" spans="1:3">
       <c r="A1378">
-        <v>9519071</v>
-      </c>
-      <c r="B1378" s="3" t="s">
-        <v>1070</v>
+        <v>9519031</v>
+      </c>
+      <c r="B1378" t="s">
+        <v>1030</v>
       </c>
       <c r="C1378" t="s">
         <v>891</v>
@@ -17832,10 +18194,10 @@
     </row>
     <row r="1379" spans="1:3">
       <c r="A1379">
-        <v>9519075</v>
-      </c>
-      <c r="B1379" s="3" t="s">
-        <v>1071</v>
+        <v>9519071</v>
+      </c>
+      <c r="B1379" t="s">
+        <v>1031</v>
       </c>
       <c r="C1379" t="s">
         <v>891</v>
@@ -17843,10 +18205,10 @@
     </row>
     <row r="1380" spans="1:3">
       <c r="A1380">
-        <v>9519078</v>
-      </c>
-      <c r="B1380" s="3" t="s">
-        <v>13</v>
+        <v>9519075</v>
+      </c>
+      <c r="B1380" t="s">
+        <v>1032</v>
       </c>
       <c r="C1380" t="s">
         <v>891</v>
@@ -17854,29 +18216,438 @@
     </row>
     <row r="1381" spans="1:3">
       <c r="A1381">
-        <v>9519085</v>
-      </c>
-      <c r="B1381" s="3" t="s">
-        <v>1072</v>
+        <v>9519078</v>
+      </c>
+      <c r="B1381" t="s">
+        <v>13</v>
       </c>
       <c r="C1381" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="1382" spans="1:3">
       <c r="A1382">
-        <v>9519130</v>
+        <v>9519085</v>
+      </c>
+      <c r="B1382" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C1382" t="s">
+        <v>892</v>
       </c>
     </row>
     <row r="1383" spans="1:3">
       <c r="A1383">
+        <v>9519130</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:3">
+      <c r="A1384">
         <v>9519144</v>
       </c>
     </row>
+    <row r="1385" spans="1:3">
+      <c r="A1385">
+        <v>9519361</v>
+      </c>
+      <c r="B1385" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C1385" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:3">
+      <c r="A1386">
+        <v>9519363</v>
+      </c>
+      <c r="B1386" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C1386" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:3">
+      <c r="A1387">
+        <v>9519366</v>
+      </c>
+      <c r="B1387" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C1387" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:3">
+      <c r="A1388">
+        <v>9519375</v>
+      </c>
+      <c r="B1388" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C1388" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:3">
+      <c r="A1389">
+        <v>9519376</v>
+      </c>
+      <c r="B1389" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C1389" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:3">
+      <c r="A1390">
+        <v>9519377</v>
+      </c>
+      <c r="B1390" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C1390" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:3">
+      <c r="A1391">
+        <v>9519416</v>
+      </c>
+      <c r="B1391" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C1391" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:3">
+      <c r="A1392">
+        <v>9519422</v>
+      </c>
+      <c r="B1392" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C1392" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:3">
+      <c r="A1393">
+        <v>9519423</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:3">
+      <c r="A1394">
+        <v>9519425</v>
+      </c>
+      <c r="B1394" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C1394" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:3">
+      <c r="A1395">
+        <v>9519426</v>
+      </c>
+      <c r="B1395" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C1395" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:3">
+      <c r="A1396">
+        <v>9519427</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:3">
+      <c r="A1397">
+        <v>9519428</v>
+      </c>
+      <c r="B1397" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C1397" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:3">
+      <c r="A1398">
+        <v>9519431</v>
+      </c>
+      <c r="B1398" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C1398" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:3">
+      <c r="A1399">
+        <v>9519433</v>
+      </c>
+      <c r="B1399" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C1399" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:3">
+      <c r="A1400">
+        <v>9519459</v>
+      </c>
+      <c r="B1400" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C1400" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:3">
+      <c r="A1401">
+        <v>9519460</v>
+      </c>
+      <c r="B1401" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C1401" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:3">
+      <c r="A1402">
+        <v>9519461</v>
+      </c>
+      <c r="B1402" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C1402" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:3">
+      <c r="A1403">
+        <v>9519462</v>
+      </c>
+      <c r="B1403" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C1403" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:3">
+      <c r="A1404">
+        <v>9519606</v>
+      </c>
+      <c r="B1404" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C1404" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:3">
+      <c r="A1405">
+        <v>9519613</v>
+      </c>
+      <c r="B1405" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C1405" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:3">
+      <c r="A1406">
+        <v>9519614</v>
+      </c>
+      <c r="B1406" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C1406" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:3">
+      <c r="A1407">
+        <v>9519616</v>
+      </c>
+      <c r="B1407" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C1407" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:3">
+      <c r="A1408">
+        <v>9519635</v>
+      </c>
+      <c r="B1408" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C1408" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:3">
+      <c r="A1409">
+        <v>9519700</v>
+      </c>
+      <c r="B1409" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C1409" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:3">
+      <c r="A1410">
+        <v>9519701</v>
+      </c>
+      <c r="B1410" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C1410" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:3">
+      <c r="A1411">
+        <v>9519702</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:3">
+      <c r="A1412">
+        <v>9519714</v>
+      </c>
+      <c r="B1412" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C1412" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:3">
+      <c r="A1413">
+        <v>9519715</v>
+      </c>
+      <c r="B1413" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C1413" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:3">
+      <c r="A1414">
+        <v>9519716</v>
+      </c>
+      <c r="B1414" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C1414" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:3">
+      <c r="A1415">
+        <v>9519717</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:3">
+      <c r="A1416">
+        <v>9519718</v>
+      </c>
+      <c r="B1416" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C1416" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:3">
+      <c r="A1417">
+        <v>9519719</v>
+      </c>
+      <c r="B1417" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C1417" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:3">
+      <c r="A1418">
+        <v>9519720</v>
+      </c>
+      <c r="B1418" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C1418" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:3">
+      <c r="A1419">
+        <v>9519980</v>
+      </c>
+      <c r="B1419" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C1419" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:3">
+      <c r="A1420">
+        <v>9520680</v>
+      </c>
+      <c r="B1420" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C1420" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:3">
+      <c r="A1421">
+        <v>9520689</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:3">
+      <c r="A1422">
+        <v>9520736</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:3">
+      <c r="A1423">
+        <v>9520739</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:3">
+      <c r="A1424">
+        <v>9520838</v>
+      </c>
+      <c r="B1424" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C1424" t="s">
+        <v>891</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C1383">
-    <sortState ref="A2:C1383">
-      <sortCondition ref="A1:A1338"/>
+  <autoFilter ref="A1:C1424">
+    <sortState ref="A2:C1384">
+      <sortCondition ref="A1:A1383"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
